--- a/concert/Бюджет_концерта.xlsx
+++ b/concert/Бюджет_концерта.xlsx
@@ -35,7 +35,21 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B19" authorId="0">
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">«Валовой сбор» — 5% считается со всей кассы.
+«Сбор после вычета УСН» — 5% считается с того, что осталось после УСН 6%.
+На базовых цифрах разница около 1 400 ₽. Проверьте формулировку в договоре с оператором.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="397">
   <si>
     <t xml:space="preserve">КОНЦЕРТ: ИТОГОВАЯ ЭКОНОМИКА</t>
   </si>
@@ -78,6 +92,9 @@
     <t xml:space="preserve">Налоги УСН 6%</t>
   </si>
   <si>
+    <t xml:space="preserve">Комиссия за продажу билетов 5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">Отчисления в РАО 8%</t>
   </si>
   <si>
@@ -87,6 +104,9 @@
     <t xml:space="preserve">Средняя цена платного билета</t>
   </si>
   <si>
+    <t xml:space="preserve">Заполняемость зала</t>
+  </si>
+  <si>
     <t xml:space="preserve">ПРИБЫЛЬ (делится пополам)</t>
   </si>
   <si>
@@ -246,6 +266,18 @@
     <t xml:space="preserve">Начисляется на весь валовой сбор</t>
   </si>
   <si>
+    <t xml:space="preserve">Комиссия за продажу билетов, %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вычитается сразу после УСН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">База для комиссии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Операторы обычно берут процент от номинала билета, то есть от валового сбора</t>
+  </si>
+  <si>
     <t xml:space="preserve">Отчисления в РАО, %</t>
   </si>
   <si>
@@ -588,12 +620,6 @@
     <t xml:space="preserve">Этап 2 — вычитается из половины прибыли организатора. Резерв считается процентом от суммы строк выше.</t>
   </si>
   <si>
-    <t xml:space="preserve">Комиссия билетного оператора</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ВАЖНО: если оператор удерживает её из кассы, она относится к этапу 1 — скажите, и перенесу</t>
-  </si>
-  <si>
     <t xml:space="preserve">Полиграфия: афиши, флаеры</t>
   </si>
   <si>
@@ -822,13 +848,19 @@
     <t xml:space="preserve">Ставка — на листе «Вводные»</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Отчисления в РАО 8%</t>
+    <t xml:space="preserve">3. Комиссия за продажу билетов 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">База — валовой сбор или сбор после вычета УСН, переключатель на листе «Вводные»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Отчисления в РАО 8%</t>
   </si>
   <si>
     <t xml:space="preserve">Ставка 8% по вашим условиям. Базовый тариф РАО для концертов обычно 5% — стоит сверить с договором</t>
   </si>
   <si>
-    <t xml:space="preserve">4. Технические расходы: аренда звука и обеспечение площадки</t>
+    <t xml:space="preserve">5. Технические расходы: аренда звука и обеспечение площадки</t>
   </si>
   <si>
     <t xml:space="preserve">Режим «из сметы» или «фиксированной суммой» — на листе «Вводные»</t>
@@ -846,7 +878,7 @@
     <t xml:space="preserve">Прочие расходы — если вычитаются до раздела</t>
   </si>
   <si>
-    <t xml:space="preserve">5. ПРИБЫЛЬ</t>
+    <t xml:space="preserve">6. ПРИБЫЛЬ</t>
   </si>
   <si>
     <t xml:space="preserve">РАЗДЕЛ ПРИБЫЛИ ПОПОЛАМ</t>
@@ -918,7 +950,7 @@
     <t xml:space="preserve">Пессимистичный и оптимистичный задаются на листе «Вводные»</t>
   </si>
   <si>
-    <t xml:space="preserve">4. Технические расходы</t>
+    <t xml:space="preserve">5. Технические расходы</t>
   </si>
   <si>
     <t xml:space="preserve">   гонорары — если до раздела</t>
@@ -1638,6 +1670,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1647,10 +1683,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2314,7 +2346,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2422,7 +2454,7 @@
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">Экономика!$C$8</f>
-        <v>-37288</v>
+        <v>-23305</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2432,70 +2464,70 @@
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">Экономика!$C$9</f>
-        <v>-154500</v>
+        <v>-37288</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F9" s="11" t="n">
+        <f aca="false">Экономика!$C$10</f>
+        <v>-154500</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <f aca="false">Билеты!$B$19</f>
         <v>2427.60416666667</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <f aca="false">Экономика!$C$30</f>
-        <v>246346</v>
-      </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <f aca="false">Экономика!$C$34</f>
-        <v>123173</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="13" t="n">
+        <f aca="false">Билеты!$B$21</f>
+        <v>0.673333333333333</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="B11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <f aca="false">Экономика!$C$31</f>
+        <v>223041</v>
+      </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="E11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <f aca="false">Экономика!$C$35</f>
+        <v>111520.5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <f aca="false">Экономика!$C$37</f>
-        <v>-8622.11</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <f aca="false">Экономика!$C$38</f>
-        <v>-1231.73</v>
-      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
@@ -2503,16 +2535,16 @@
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <f aca="false">Экономика!$C$39</f>
-        <v>-49000</v>
+        <f aca="false">Экономика!$C$38</f>
+        <v>-7806.435</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="11" t="n">
-        <f aca="false">Экономика!$C$48</f>
-        <v>-60000</v>
+        <f aca="false">Экономика!$C$39</f>
+        <v>-1115.205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2521,219 +2553,227 @@
         <v>18</v>
       </c>
       <c r="C15" s="11" t="n">
-        <f aca="false">Экономика!$C$57</f>
-        <v>-76450</v>
+        <f aca="false">Экономика!$C$40</f>
+        <v>-49000</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="10" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="11" t="n">
-        <f aca="false">Экономика!$C$37+Экономика!$C$38+Экономика!$C$39+Экономика!$C$48+Экономика!$C$57</f>
-        <v>-195303.84</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">Экономика!$C$49</f>
+        <v>-60000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="11" t="n">
+        <f aca="false">Экономика!$C$58</f>
+        <v>-76450</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <f aca="false">Экономика!$C$38+Экономика!$C$39+Экономика!$C$40+Экономика!$C$49+Экономика!$C$58</f>
+        <v>-194371.64</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="15" t="n">
         <f aca="false">Экономика!$C$72</f>
-        <v>-72130.84</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="15" t="n">
+        <v>-82851.14</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="16" t="n">
         <f aca="false">Экономика!$C$81</f>
-        <v>-0.154754001287277</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+        <v>-0.177754001287277</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="B19" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <f aca="false">Экономика!$C$77</f>
-        <v>648432.760364004</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="12" t="n">
-        <f aca="false">Экономика!$C$78</f>
-        <v>268</v>
-      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
       <c r="B20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <f aca="false">Экономика!$C$79</f>
-        <v>0.939861111111111</v>
+      <c r="C20" s="11" t="n">
+        <f aca="false">Экономика!$C$77</f>
+        <v>688459.47396672</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="12" t="n">
+        <f aca="false">Экономика!$C$78</f>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <f aca="false">Экономика!$C$79</f>
+        <v>0.995972222222222</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="13" t="n">
         <f aca="false">Экономика!$C$80</f>
-        <v>-0.395833333333333</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>-0.479166666666667</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
-      <c r="B22" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="18" t="str">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4"/>
+      <c r="B23" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="18" t="str">
         <f aca="false">Экономика!$C$83</f>
-        <v>УБЫТОК. Нужен сбор от 648 433 ₽ (94% зала), чтобы выйти в ноль</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4"/>
-      <c r="B25" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="19" t="s">
+        <v>УБЫТОК. Нужен сбор от 688 459 ₽ (100% зала), чтобы выйти в ноль</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4"/>
+      <c r="B26" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="C26" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4"/>
-      <c r="B26" s="20" t="n">
-        <f aca="false">Сценарии!B24</f>
-        <v>-147038.93625</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <f aca="false">Сценарии!C24</f>
-        <v>-72130.84</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <f aca="false">Сценарии!D24</f>
-        <v>-9707.42645833336</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <f aca="false">Сценарии!E24</f>
-        <v>17182.659375</v>
+      <c r="D26" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="20" t="n">
+        <f aca="false">Сценарии!B25</f>
+        <v>-153404.114375</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <f aca="false">Сценарии!C25</f>
+        <v>-82851.14</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <f aca="false">Сценарии!D25</f>
+        <v>-24056.9946875</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <f aca="false">Сценарии!E25</f>
+        <v>1269.71406249999</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4"/>
+      <c r="B28" s="21" t="n">
         <f aca="false">Сценарии!B5</f>
         <v>0.4</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C28" s="21" t="n">
         <f aca="false">Сценарии!C5</f>
         <v>0.673333333333333</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D28" s="21" t="n">
         <f aca="false">Сценарии!D5</f>
         <v>0.9</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E28" s="21" t="n">
         <f aca="false">Сценарии!E5</f>
         <v>1</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
-      <c r="B30" s="22" t="s">
+      <c r="F28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="22"/>
@@ -2743,7 +2783,7 @@
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
@@ -2753,7 +2793,7 @@
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
@@ -2763,7 +2803,7 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
       <c r="B34" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
@@ -2773,7 +2813,7 @@
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
       <c r="B35" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" s="22"/>
       <c r="D35" s="22"/>
@@ -2783,33 +2823,43 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
       <c r="B36" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C36" s="22"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
     </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4"/>
+      <c r="B37" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
   </mergeCells>
-  <conditionalFormatting sqref="C22">
+  <conditionalFormatting sqref="C23">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT($C$22,6)="УБЫТОК"</formula>
+      <formula>LEFT($C$23,6)="УБЫТОК"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEFT($C$22,7)="ЗДОРОВО"</formula>
+      <formula>LEFT($C$23,7)="ЗДОРОВО"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:E26">
+  <conditionalFormatting sqref="B27:E27">
     <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2838,7 +2888,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2850,7 +2900,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2872,7 +2922,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="89" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2884,7 +2934,7 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B5" s="90" t="n">
         <v>1500</v>
@@ -2913,32 +2963,32 @@
         <v>0.3</v>
       </c>
       <c r="B6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>-44147.5247524753</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>-50563.3663366337</v>
       </c>
       <c r="C6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>-7363.36633663368</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>-15917.8217821782</v>
       </c>
       <c r="D6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>29420.7920792079</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>18727.7227722772</v>
       </c>
       <c r="E6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>66204.9504950495</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>53373.2673267326</v>
       </c>
       <c r="F6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>102989.108910891</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>88018.8118811881</v>
       </c>
       <c r="G6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>139773.267326733</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>122664.356435644</v>
       </c>
       <c r="H6" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>176557.425742574</v>
+        <f aca="false">(Вводные!$B$12*$A6*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>157309.900990099</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2946,32 +2996,32 @@
         <v>0.4</v>
       </c>
       <c r="B7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>-7363.36633663368</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>-15917.8217821782</v>
       </c>
       <c r="C7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>41682.1782178218</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>30276.2376237623</v>
       </c>
       <c r="D7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>90727.7227722772</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>76470.297029703</v>
       </c>
       <c r="E7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>139773.267326733</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>122664.356435644</v>
       </c>
       <c r="F7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>188818.811881188</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>168858.415841584</v>
       </c>
       <c r="G7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>237864.356435644</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>215052.475247525</v>
       </c>
       <c r="H7" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>286909.900990099</v>
+        <f aca="false">(Вводные!$B$12*$A7*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>261246.534653465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2979,32 +3029,32 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>29420.7920792079</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>18727.7227722772</v>
       </c>
       <c r="C8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>90727.7227722772</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>76470.297029703</v>
       </c>
       <c r="D8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>152034.653465347</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>134212.871287129</v>
       </c>
       <c r="E8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>213341.584158416</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>191955.445544554</v>
       </c>
       <c r="F8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>274648.514851485</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>249698.01980198</v>
       </c>
       <c r="G8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>335955.445544554</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>307440.594059406</v>
       </c>
       <c r="H8" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>397262.376237624</v>
+        <f aca="false">(Вводные!$B$12*$A8*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>365183.168316832</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3012,32 +3062,32 @@
         <v>0.6</v>
       </c>
       <c r="B9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>66204.9504950495</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>53373.2673267326</v>
       </c>
       <c r="C9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>139773.267326733</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>122664.356435644</v>
       </c>
       <c r="D9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>213341.584158416</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>191955.445544554</v>
       </c>
       <c r="E9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>286909.900990099</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>261246.534653465</v>
       </c>
       <c r="F9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>360478.217821782</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>330537.623762376</v>
       </c>
       <c r="G9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>434046.534653465</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>399828.712871287</v>
       </c>
       <c r="H9" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>507614.851485148</v>
+        <f aca="false">(Вводные!$B$12*$A9*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>469119.801980198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,32 +3095,32 @@
         <v>0.7</v>
       </c>
       <c r="B10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>102989.108910891</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>88018.8118811881</v>
       </c>
       <c r="C10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>188818.811881188</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>168858.415841584</v>
       </c>
       <c r="D10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>274648.514851485</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>249698.01980198</v>
       </c>
       <c r="E10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>360478.217821782</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>330537.623762376</v>
       </c>
       <c r="F10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>446307.920792079</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>411377.227722772</v>
       </c>
       <c r="G10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>532137.623762376</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>492216.831683168</v>
       </c>
       <c r="H10" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>617967.326732673</v>
+        <f aca="false">(Вводные!$B$12*$A10*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>573056.435643564</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3078,32 +3128,32 @@
         <v>0.8</v>
       </c>
       <c r="B11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>139773.267326733</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>122664.356435644</v>
       </c>
       <c r="C11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>237864.356435644</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>215052.475247525</v>
       </c>
       <c r="D11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>335955.445544554</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>307440.594059406</v>
       </c>
       <c r="E11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>434046.534653465</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>399828.712871287</v>
       </c>
       <c r="F11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>532137.623762376</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>492216.831683168</v>
       </c>
       <c r="G11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>630228.712871287</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>584604.950495049</v>
       </c>
       <c r="H11" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>728319.801980198</v>
+        <f aca="false">(Вводные!$B$12*$A11*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>676993.069306931</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3111,32 +3161,32 @@
         <v>0.9</v>
       </c>
       <c r="B12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>176557.425742574</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>157309.900990099</v>
       </c>
       <c r="C12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>286909.900990099</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>261246.534653465</v>
       </c>
       <c r="D12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>397262.376237624</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>365183.168316832</v>
       </c>
       <c r="E12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>507614.851485149</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>469119.801980198</v>
       </c>
       <c r="F12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>617967.326732673</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>573056.435643564</v>
       </c>
       <c r="G12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>728319.801980198</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>676993.069306931</v>
       </c>
       <c r="H12" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>838672.277227723</v>
+        <f aca="false">(Вводные!$B$12*$A12*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>780929.702970297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3144,32 +3194,32 @@
         <v>1</v>
       </c>
       <c r="B13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>213341.584158416</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*B$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>191955.445544554</v>
       </c>
       <c r="C13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>335955.445544554</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*C$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>307440.594059406</v>
       </c>
       <c r="D13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>458569.306930693</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*D$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>422925.742574257</v>
       </c>
       <c r="E13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>581183.168316832</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*E$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>538410.891089109</v>
       </c>
       <c r="F13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>703797.02970297</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*F$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>653896.03960396</v>
       </c>
       <c r="G13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>826410.891089109</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*G$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>769381.188118812</v>
       </c>
       <c r="H13" s="49" t="n">
-        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$19)-Экономика!$C$75</f>
-        <v>949024.752475248</v>
+        <f aca="false">(Вводные!$B$12*$A13*Билеты!$B$22*H$5)*(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18))-Экономика!$C$75</f>
+        <v>884866.336633663</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3184,7 +3234,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="89" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -3196,7 +3246,7 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B16" s="90" t="n">
         <v>1500</v>
@@ -3225,32 +3275,32 @@
         <v>0.3</v>
       </c>
       <c r="B17" s="49" t="n">
-        <f aca="false">IF(B6&gt;=0,B6*Вводные!$B$26,IF(Вводные!$B$28="Да",B6*Вводные!$B$26,B6))-MAX(0,IF(B6&gt;=0,B6*Вводные!$B$26,IF(Вводные!$B$28="Да",B6*Вводные!$B$26,B6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-229597.524752475</v>
+        <f aca="false">IF(B6&gt;=0,B6*Вводные!$B$28,IF(Вводные!$B$30="Да",B6*Вводные!$B$28,B6))-MAX(0,IF(B6&gt;=0,B6*Вводные!$B$28,IF(Вводные!$B$30="Да",B6*Вводные!$B$28,B6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-236013.366336634</v>
       </c>
       <c r="C17" s="49" t="n">
-        <f aca="false">IF(C6&gt;=0,C6*Вводные!$B$26,IF(Вводные!$B$28="Да",C6*Вводные!$B$26,C6))-MAX(0,IF(C6&gt;=0,C6*Вводные!$B$26,IF(Вводные!$B$28="Да",C6*Вводные!$B$26,C6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-192813.366336634</v>
+        <f aca="false">IF(C6&gt;=0,C6*Вводные!$B$28,IF(Вводные!$B$30="Да",C6*Вводные!$B$28,C6))-MAX(0,IF(C6&gt;=0,C6*Вводные!$B$28,IF(Вводные!$B$30="Да",C6*Вводные!$B$28,C6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-201367.821782178</v>
       </c>
       <c r="D17" s="49" t="n">
-        <f aca="false">IF(D6&gt;=0,D6*Вводные!$B$26,IF(Вводные!$B$28="Да",D6*Вводные!$B$26,D6))-MAX(0,IF(D6&gt;=0,D6*Вводные!$B$26,IF(Вводные!$B$28="Да",D6*Вводные!$B$26,D6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-171916.435643564</v>
+        <f aca="false">IF(D6&gt;=0,D6*Вводные!$B$28,IF(Вводные!$B$30="Да",D6*Вводные!$B$28,D6))-MAX(0,IF(D6&gt;=0,D6*Вводные!$B$28,IF(Вводные!$B$30="Да",D6*Вводные!$B$28,D6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-176835.247524752</v>
       </c>
       <c r="E17" s="49" t="n">
-        <f aca="false">IF(E6&gt;=0,E6*Вводные!$B$26,IF(Вводные!$B$28="Да",E6*Вводные!$B$26,E6))-MAX(0,IF(E6&gt;=0,E6*Вводные!$B$26,IF(Вводные!$B$28="Да",E6*Вводные!$B$26,E6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-154995.722772277</v>
+        <f aca="false">IF(E6&gt;=0,E6*Вводные!$B$28,IF(Вводные!$B$30="Да",E6*Вводные!$B$28,E6))-MAX(0,IF(E6&gt;=0,E6*Вводные!$B$28,IF(Вводные!$B$30="Да",E6*Вводные!$B$28,E6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-160898.297029703</v>
       </c>
       <c r="F17" s="49" t="n">
-        <f aca="false">IF(F6&gt;=0,F6*Вводные!$B$26,IF(Вводные!$B$28="Да",F6*Вводные!$B$26,F6))-MAX(0,IF(F6&gt;=0,F6*Вводные!$B$26,IF(Вводные!$B$28="Да",F6*Вводные!$B$26,F6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-138075.00990099</v>
+        <f aca="false">IF(F6&gt;=0,F6*Вводные!$B$28,IF(Вводные!$B$30="Да",F6*Вводные!$B$28,F6))-MAX(0,IF(F6&gt;=0,F6*Вводные!$B$28,IF(Вводные!$B$30="Да",F6*Вводные!$B$28,F6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-144961.346534653</v>
       </c>
       <c r="G17" s="49" t="n">
-        <f aca="false">IF(G6&gt;=0,G6*Вводные!$B$26,IF(Вводные!$B$28="Да",G6*Вводные!$B$26,G6))-MAX(0,IF(G6&gt;=0,G6*Вводные!$B$26,IF(Вводные!$B$28="Да",G6*Вводные!$B$26,G6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-121154.297029703</v>
+        <f aca="false">IF(G6&gt;=0,G6*Вводные!$B$28,IF(Вводные!$B$30="Да",G6*Вводные!$B$28,G6))-MAX(0,IF(G6&gt;=0,G6*Вводные!$B$28,IF(Вводные!$B$30="Да",G6*Вводные!$B$28,G6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-129024.396039604</v>
       </c>
       <c r="H17" s="49" t="n">
-        <f aca="false">IF(H6&gt;=0,H6*Вводные!$B$26,IF(Вводные!$B$28="Да",H6*Вводные!$B$26,H6))-MAX(0,IF(H6&gt;=0,H6*Вводные!$B$26,IF(Вводные!$B$28="Да",H6*Вводные!$B$26,H6)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-104233.584158416</v>
+        <f aca="false">IF(H6&gt;=0,H6*Вводные!$B$28,IF(Вводные!$B$30="Да",H6*Вводные!$B$28,H6))-MAX(0,IF(H6&gt;=0,H6*Вводные!$B$28,IF(Вводные!$B$30="Да",H6*Вводные!$B$28,H6)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-113087.445544554</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3258,32 +3308,32 @@
         <v>0.4</v>
       </c>
       <c r="B18" s="49" t="n">
-        <f aca="false">IF(B7&gt;=0,B7*Вводные!$B$26,IF(Вводные!$B$28="Да",B7*Вводные!$B$26,B7))-MAX(0,IF(B7&gt;=0,B7*Вводные!$B$26,IF(Вводные!$B$28="Да",B7*Вводные!$B$26,B7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-192813.366336634</v>
+        <f aca="false">IF(B7&gt;=0,B7*Вводные!$B$28,IF(Вводные!$B$30="Да",B7*Вводные!$B$28,B7))-MAX(0,IF(B7&gt;=0,B7*Вводные!$B$28,IF(Вводные!$B$30="Да",B7*Вводные!$B$28,B7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-201367.821782178</v>
       </c>
       <c r="C18" s="49" t="n">
-        <f aca="false">IF(C7&gt;=0,C7*Вводные!$B$26,IF(Вводные!$B$28="Да",C7*Вводные!$B$26,C7))-MAX(0,IF(C7&gt;=0,C7*Вводные!$B$26,IF(Вводные!$B$28="Да",C7*Вводные!$B$26,C7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-166276.198019802</v>
+        <f aca="false">IF(C7&gt;=0,C7*Вводные!$B$28,IF(Вводные!$B$30="Да",C7*Вводные!$B$28,C7))-MAX(0,IF(C7&gt;=0,C7*Вводные!$B$28,IF(Вводные!$B$30="Да",C7*Вводные!$B$28,C7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-171522.930693069</v>
       </c>
       <c r="D18" s="49" t="n">
-        <f aca="false">IF(D7&gt;=0,D7*Вводные!$B$26,IF(Вводные!$B$28="Да",D7*Вводные!$B$26,D7))-MAX(0,IF(D7&gt;=0,D7*Вводные!$B$26,IF(Вводные!$B$28="Да",D7*Вводные!$B$26,D7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-143715.247524752</v>
+        <f aca="false">IF(D7&gt;=0,D7*Вводные!$B$28,IF(Вводные!$B$30="Да",D7*Вводные!$B$28,D7))-MAX(0,IF(D7&gt;=0,D7*Вводные!$B$28,IF(Вводные!$B$30="Да",D7*Вводные!$B$28,D7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-150273.663366337</v>
       </c>
       <c r="E18" s="49" t="n">
-        <f aca="false">IF(E7&gt;=0,E7*Вводные!$B$26,IF(Вводные!$B$28="Да",E7*Вводные!$B$26,E7))-MAX(0,IF(E7&gt;=0,E7*Вводные!$B$26,IF(Вводные!$B$28="Да",E7*Вводные!$B$26,E7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-121154.297029703</v>
+        <f aca="false">IF(E7&gt;=0,E7*Вводные!$B$28,IF(Вводные!$B$30="Да",E7*Вводные!$B$28,E7))-MAX(0,IF(E7&gt;=0,E7*Вводные!$B$28,IF(Вводные!$B$30="Да",E7*Вводные!$B$28,E7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-129024.396039604</v>
       </c>
       <c r="F18" s="49" t="n">
-        <f aca="false">IF(F7&gt;=0,F7*Вводные!$B$26,IF(Вводные!$B$28="Да",F7*Вводные!$B$26,F7))-MAX(0,IF(F7&gt;=0,F7*Вводные!$B$26,IF(Вводные!$B$28="Да",F7*Вводные!$B$26,F7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-98593.3465346535</v>
+        <f aca="false">IF(F7&gt;=0,F7*Вводные!$B$28,IF(Вводные!$B$30="Да",F7*Вводные!$B$28,F7))-MAX(0,IF(F7&gt;=0,F7*Вводные!$B$28,IF(Вводные!$B$30="Да",F7*Вводные!$B$28,F7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-107775.128712871</v>
       </c>
       <c r="G18" s="49" t="n">
-        <f aca="false">IF(G7&gt;=0,G7*Вводные!$B$26,IF(Вводные!$B$28="Да",G7*Вводные!$B$26,G7))-MAX(0,IF(G7&gt;=0,G7*Вводные!$B$26,IF(Вводные!$B$28="Да",G7*Вводные!$B$26,G7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-76032.396039604</v>
+        <f aca="false">IF(G7&gt;=0,G7*Вводные!$B$28,IF(Вводные!$B$30="Да",G7*Вводные!$B$28,G7))-MAX(0,IF(G7&gt;=0,G7*Вводные!$B$28,IF(Вводные!$B$30="Да",G7*Вводные!$B$28,G7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-86525.8613861387</v>
       </c>
       <c r="H18" s="49" t="n">
-        <f aca="false">IF(H7&gt;=0,H7*Вводные!$B$26,IF(Вводные!$B$28="Да",H7*Вводные!$B$26,H7))-MAX(0,IF(H7&gt;=0,H7*Вводные!$B$26,IF(Вводные!$B$28="Да",H7*Вводные!$B$26,H7)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-53471.4455445545</v>
+        <f aca="false">IF(H7&gt;=0,H7*Вводные!$B$28,IF(Вводные!$B$30="Да",H7*Вводные!$B$28,H7))-MAX(0,IF(H7&gt;=0,H7*Вводные!$B$28,IF(Вводные!$B$30="Да",H7*Вводные!$B$28,H7)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-65276.594059406</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3291,32 +3341,32 @@
         <v>0.5</v>
       </c>
       <c r="B19" s="49" t="n">
-        <f aca="false">IF(B8&gt;=0,B8*Вводные!$B$26,IF(Вводные!$B$28="Да",B8*Вводные!$B$26,B8))-MAX(0,IF(B8&gt;=0,B8*Вводные!$B$26,IF(Вводные!$B$28="Да",B8*Вводные!$B$26,B8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-171916.435643564</v>
+        <f aca="false">IF(B8&gt;=0,B8*Вводные!$B$28,IF(Вводные!$B$30="Да",B8*Вводные!$B$28,B8))-MAX(0,IF(B8&gt;=0,B8*Вводные!$B$28,IF(Вводные!$B$30="Да",B8*Вводные!$B$28,B8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-176835.247524752</v>
       </c>
       <c r="C19" s="49" t="n">
-        <f aca="false">IF(C8&gt;=0,C8*Вводные!$B$26,IF(Вводные!$B$28="Да",C8*Вводные!$B$26,C8))-MAX(0,IF(C8&gt;=0,C8*Вводные!$B$26,IF(Вводные!$B$28="Да",C8*Вводные!$B$26,C8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-143715.247524752</v>
+        <f aca="false">IF(C8&gt;=0,C8*Вводные!$B$28,IF(Вводные!$B$30="Да",C8*Вводные!$B$28,C8))-MAX(0,IF(C8&gt;=0,C8*Вводные!$B$28,IF(Вводные!$B$30="Да",C8*Вводные!$B$28,C8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-150273.663366337</v>
       </c>
       <c r="D19" s="49" t="n">
-        <f aca="false">IF(D8&gt;=0,D8*Вводные!$B$26,IF(Вводные!$B$28="Да",D8*Вводные!$B$26,D8))-MAX(0,IF(D8&gt;=0,D8*Вводные!$B$26,IF(Вводные!$B$28="Да",D8*Вводные!$B$26,D8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-115514.059405941</v>
+        <f aca="false">IF(D8&gt;=0,D8*Вводные!$B$28,IF(Вводные!$B$30="Да",D8*Вводные!$B$28,D8))-MAX(0,IF(D8&gt;=0,D8*Вводные!$B$28,IF(Вводные!$B$30="Да",D8*Вводные!$B$28,D8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-123712.079207921</v>
       </c>
       <c r="E19" s="49" t="n">
-        <f aca="false">IF(E8&gt;=0,E8*Вводные!$B$26,IF(Вводные!$B$28="Да",E8*Вводные!$B$26,E8))-MAX(0,IF(E8&gt;=0,E8*Вводные!$B$26,IF(Вводные!$B$28="Да",E8*Вводные!$B$26,E8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-87312.8712871287</v>
+        <f aca="false">IF(E8&gt;=0,E8*Вводные!$B$28,IF(Вводные!$B$30="Да",E8*Вводные!$B$28,E8))-MAX(0,IF(E8&gt;=0,E8*Вводные!$B$28,IF(Вводные!$B$30="Да",E8*Вводные!$B$28,E8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-97150.495049505</v>
       </c>
       <c r="F19" s="49" t="n">
-        <f aca="false">IF(F8&gt;=0,F8*Вводные!$B$26,IF(Вводные!$B$28="Да",F8*Вводные!$B$26,F8))-MAX(0,IF(F8&gt;=0,F8*Вводные!$B$26,IF(Вводные!$B$28="Да",F8*Вводные!$B$26,F8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-59111.6831683169</v>
+        <f aca="false">IF(F8&gt;=0,F8*Вводные!$B$28,IF(Вводные!$B$30="Да",F8*Вводные!$B$28,F8))-MAX(0,IF(F8&gt;=0,F8*Вводные!$B$28,IF(Вводные!$B$30="Да",F8*Вводные!$B$28,F8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-70588.9108910892</v>
       </c>
       <c r="G19" s="49" t="n">
-        <f aca="false">IF(G8&gt;=0,G8*Вводные!$B$26,IF(Вводные!$B$28="Да",G8*Вводные!$B$26,G8))-MAX(0,IF(G8&gt;=0,G8*Вводные!$B$26,IF(Вводные!$B$28="Да",G8*Вводные!$B$26,G8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-30910.495049505</v>
+        <f aca="false">IF(G8&gt;=0,G8*Вводные!$B$28,IF(Вводные!$B$30="Да",G8*Вводные!$B$28,G8))-MAX(0,IF(G8&gt;=0,G8*Вводные!$B$28,IF(Вводные!$B$30="Да",G8*Вводные!$B$28,G8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-44027.3267326733</v>
       </c>
       <c r="H19" s="49" t="n">
-        <f aca="false">IF(H8&gt;=0,H8*Вводные!$B$26,IF(Вводные!$B$28="Да",H8*Вводные!$B$26,H8))-MAX(0,IF(H8&gt;=0,H8*Вводные!$B$26,IF(Вводные!$B$28="Да",H8*Вводные!$B$26,H8)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-2709.30693069307</v>
+        <f aca="false">IF(H8&gt;=0,H8*Вводные!$B$28,IF(Вводные!$B$30="Да",H8*Вводные!$B$28,H8))-MAX(0,IF(H8&gt;=0,H8*Вводные!$B$28,IF(Вводные!$B$30="Да",H8*Вводные!$B$28,H8)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-17465.7425742575</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3324,32 +3374,32 @@
         <v>0.6</v>
       </c>
       <c r="B20" s="49" t="n">
-        <f aca="false">IF(B9&gt;=0,B9*Вводные!$B$26,IF(Вводные!$B$28="Да",B9*Вводные!$B$26,B9))-MAX(0,IF(B9&gt;=0,B9*Вводные!$B$26,IF(Вводные!$B$28="Да",B9*Вводные!$B$26,B9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-154995.722772277</v>
+        <f aca="false">IF(B9&gt;=0,B9*Вводные!$B$28,IF(Вводные!$B$30="Да",B9*Вводные!$B$28,B9))-MAX(0,IF(B9&gt;=0,B9*Вводные!$B$28,IF(Вводные!$B$30="Да",B9*Вводные!$B$28,B9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-160898.297029703</v>
       </c>
       <c r="C20" s="49" t="n">
-        <f aca="false">IF(C9&gt;=0,C9*Вводные!$B$26,IF(Вводные!$B$28="Да",C9*Вводные!$B$26,C9))-MAX(0,IF(C9&gt;=0,C9*Вводные!$B$26,IF(Вводные!$B$28="Да",C9*Вводные!$B$26,C9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-121154.297029703</v>
+        <f aca="false">IF(C9&gt;=0,C9*Вводные!$B$28,IF(Вводные!$B$30="Да",C9*Вводные!$B$28,C9))-MAX(0,IF(C9&gt;=0,C9*Вводные!$B$28,IF(Вводные!$B$30="Да",C9*Вводные!$B$28,C9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-129024.396039604</v>
       </c>
       <c r="D20" s="49" t="n">
-        <f aca="false">IF(D9&gt;=0,D9*Вводные!$B$26,IF(Вводные!$B$28="Да",D9*Вводные!$B$26,D9))-MAX(0,IF(D9&gt;=0,D9*Вводные!$B$26,IF(Вводные!$B$28="Да",D9*Вводные!$B$26,D9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-87312.8712871287</v>
+        <f aca="false">IF(D9&gt;=0,D9*Вводные!$B$28,IF(Вводные!$B$30="Да",D9*Вводные!$B$28,D9))-MAX(0,IF(D9&gt;=0,D9*Вводные!$B$28,IF(Вводные!$B$30="Да",D9*Вводные!$B$28,D9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-97150.495049505</v>
       </c>
       <c r="E20" s="49" t="n">
-        <f aca="false">IF(E9&gt;=0,E9*Вводные!$B$26,IF(Вводные!$B$28="Да",E9*Вводные!$B$26,E9))-MAX(0,IF(E9&gt;=0,E9*Вводные!$B$26,IF(Вводные!$B$28="Да",E9*Вводные!$B$26,E9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-53471.4455445545</v>
+        <f aca="false">IF(E9&gt;=0,E9*Вводные!$B$28,IF(Вводные!$B$30="Да",E9*Вводные!$B$28,E9))-MAX(0,IF(E9&gt;=0,E9*Вводные!$B$28,IF(Вводные!$B$30="Да",E9*Вводные!$B$28,E9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-65276.594059406</v>
       </c>
       <c r="F20" s="49" t="n">
-        <f aca="false">IF(F9&gt;=0,F9*Вводные!$B$26,IF(Вводные!$B$28="Да",F9*Вводные!$B$26,F9))-MAX(0,IF(F9&gt;=0,F9*Вводные!$B$26,IF(Вводные!$B$28="Да",F9*Вводные!$B$26,F9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-19630.0198019802</v>
+        <f aca="false">IF(F9&gt;=0,F9*Вводные!$B$28,IF(Вводные!$B$30="Да",F9*Вводные!$B$28,F9))-MAX(0,IF(F9&gt;=0,F9*Вводные!$B$28,IF(Вводные!$B$30="Да",F9*Вводные!$B$28,F9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-33402.693069307</v>
       </c>
       <c r="G20" s="49" t="n">
-        <f aca="false">IF(G9&gt;=0,G9*Вводные!$B$26,IF(Вводные!$B$28="Да",G9*Вводные!$B$26,G9))-MAX(0,IF(G9&gt;=0,G9*Вводные!$B$26,IF(Вводные!$B$28="Да",G9*Вводные!$B$26,G9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>14211.405940594</v>
+        <f aca="false">IF(G9&gt;=0,G9*Вводные!$B$28,IF(Вводные!$B$30="Да",G9*Вводные!$B$28,G9))-MAX(0,IF(G9&gt;=0,G9*Вводные!$B$28,IF(Вводные!$B$30="Да",G9*Вводные!$B$28,G9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-1528.79207920798</v>
       </c>
       <c r="H20" s="49" t="n">
-        <f aca="false">IF(H9&gt;=0,H9*Вводные!$B$26,IF(Вводные!$B$28="Да",H9*Вводные!$B$26,H9))-MAX(0,IF(H9&gt;=0,H9*Вводные!$B$26,IF(Вводные!$B$28="Да",H9*Вводные!$B$26,H9)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>48052.8316831683</v>
+        <f aca="false">IF(H9&gt;=0,H9*Вводные!$B$28,IF(Вводные!$B$30="Да",H9*Вводные!$B$28,H9))-MAX(0,IF(H9&gt;=0,H9*Вводные!$B$28,IF(Вводные!$B$30="Да",H9*Вводные!$B$28,H9)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>30345.108910891</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3357,32 +3407,32 @@
         <v>0.7</v>
       </c>
       <c r="B21" s="49" t="n">
-        <f aca="false">IF(B10&gt;=0,B10*Вводные!$B$26,IF(Вводные!$B$28="Да",B10*Вводные!$B$26,B10))-MAX(0,IF(B10&gt;=0,B10*Вводные!$B$26,IF(Вводные!$B$28="Да",B10*Вводные!$B$26,B10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-138075.00990099</v>
+        <f aca="false">IF(B10&gt;=0,B10*Вводные!$B$28,IF(Вводные!$B$30="Да",B10*Вводные!$B$28,B10))-MAX(0,IF(B10&gt;=0,B10*Вводные!$B$28,IF(Вводные!$B$30="Да",B10*Вводные!$B$28,B10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-144961.346534653</v>
       </c>
       <c r="C21" s="49" t="n">
-        <f aca="false">IF(C10&gt;=0,C10*Вводные!$B$26,IF(Вводные!$B$28="Да",C10*Вводные!$B$26,C10))-MAX(0,IF(C10&gt;=0,C10*Вводные!$B$26,IF(Вводные!$B$28="Да",C10*Вводные!$B$26,C10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-98593.3465346535</v>
+        <f aca="false">IF(C10&gt;=0,C10*Вводные!$B$28,IF(Вводные!$B$30="Да",C10*Вводные!$B$28,C10))-MAX(0,IF(C10&gt;=0,C10*Вводные!$B$28,IF(Вводные!$B$30="Да",C10*Вводные!$B$28,C10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-107775.128712871</v>
       </c>
       <c r="D21" s="49" t="n">
-        <f aca="false">IF(D10&gt;=0,D10*Вводные!$B$26,IF(Вводные!$B$28="Да",D10*Вводные!$B$26,D10))-MAX(0,IF(D10&gt;=0,D10*Вводные!$B$26,IF(Вводные!$B$28="Да",D10*Вводные!$B$26,D10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-59111.6831683169</v>
+        <f aca="false">IF(D10&gt;=0,D10*Вводные!$B$28,IF(Вводные!$B$30="Да",D10*Вводные!$B$28,D10))-MAX(0,IF(D10&gt;=0,D10*Вводные!$B$28,IF(Вводные!$B$30="Да",D10*Вводные!$B$28,D10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-70588.9108910892</v>
       </c>
       <c r="E21" s="49" t="n">
-        <f aca="false">IF(E10&gt;=0,E10*Вводные!$B$26,IF(Вводные!$B$28="Да",E10*Вводные!$B$26,E10))-MAX(0,IF(E10&gt;=0,E10*Вводные!$B$26,IF(Вводные!$B$28="Да",E10*Вводные!$B$26,E10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-19630.0198019802</v>
+        <f aca="false">IF(E10&gt;=0,E10*Вводные!$B$28,IF(Вводные!$B$30="Да",E10*Вводные!$B$28,E10))-MAX(0,IF(E10&gt;=0,E10*Вводные!$B$28,IF(Вводные!$B$30="Да",E10*Вводные!$B$28,E10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-33402.693069307</v>
       </c>
       <c r="F21" s="49" t="n">
-        <f aca="false">IF(F10&gt;=0,F10*Вводные!$B$26,IF(Вводные!$B$28="Да",F10*Вводные!$B$26,F10))-MAX(0,IF(F10&gt;=0,F10*Вводные!$B$26,IF(Вводные!$B$28="Да",F10*Вводные!$B$26,F10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>19851.6435643564</v>
+        <f aca="false">IF(F10&gt;=0,F10*Вводные!$B$28,IF(Вводные!$B$30="Да",F10*Вводные!$B$28,F10))-MAX(0,IF(F10&gt;=0,F10*Вводные!$B$28,IF(Вводные!$B$30="Да",F10*Вводные!$B$28,F10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>3783.52475247521</v>
       </c>
       <c r="G21" s="49" t="n">
-        <f aca="false">IF(G10&gt;=0,G10*Вводные!$B$26,IF(Вводные!$B$28="Да",G10*Вводные!$B$26,G10))-MAX(0,IF(G10&gt;=0,G10*Вводные!$B$26,IF(Вводные!$B$28="Да",G10*Вводные!$B$26,G10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>59333.306930693</v>
+        <f aca="false">IF(G10&gt;=0,G10*Вводные!$B$28,IF(Вводные!$B$30="Да",G10*Вводные!$B$28,G10))-MAX(0,IF(G10&gt;=0,G10*Вводные!$B$28,IF(Вводные!$B$30="Да",G10*Вводные!$B$28,G10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>40969.7425742574</v>
       </c>
       <c r="H21" s="49" t="n">
-        <f aca="false">IF(H10&gt;=0,H10*Вводные!$B$26,IF(Вводные!$B$28="Да",H10*Вводные!$B$26,H10))-MAX(0,IF(H10&gt;=0,H10*Вводные!$B$26,IF(Вводные!$B$28="Да",H10*Вводные!$B$26,H10)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>98814.9702970297</v>
+        <f aca="false">IF(H10&gt;=0,H10*Вводные!$B$28,IF(Вводные!$B$30="Да",H10*Вводные!$B$28,H10))-MAX(0,IF(H10&gt;=0,H10*Вводные!$B$28,IF(Вводные!$B$30="Да",H10*Вводные!$B$28,H10)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>78155.9603960395</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3390,32 +3440,32 @@
         <v>0.8</v>
       </c>
       <c r="B22" s="49" t="n">
-        <f aca="false">IF(B11&gt;=0,B11*Вводные!$B$26,IF(Вводные!$B$28="Да",B11*Вводные!$B$26,B11))-MAX(0,IF(B11&gt;=0,B11*Вводные!$B$26,IF(Вводные!$B$28="Да",B11*Вводные!$B$26,B11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-121154.297029703</v>
+        <f aca="false">IF(B11&gt;=0,B11*Вводные!$B$28,IF(Вводные!$B$30="Да",B11*Вводные!$B$28,B11))-MAX(0,IF(B11&gt;=0,B11*Вводные!$B$28,IF(Вводные!$B$30="Да",B11*Вводные!$B$28,B11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-129024.396039604</v>
       </c>
       <c r="C22" s="49" t="n">
-        <f aca="false">IF(C11&gt;=0,C11*Вводные!$B$26,IF(Вводные!$B$28="Да",C11*Вводные!$B$26,C11))-MAX(0,IF(C11&gt;=0,C11*Вводные!$B$26,IF(Вводные!$B$28="Да",C11*Вводные!$B$26,C11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-76032.396039604</v>
+        <f aca="false">IF(C11&gt;=0,C11*Вводные!$B$28,IF(Вводные!$B$30="Да",C11*Вводные!$B$28,C11))-MAX(0,IF(C11&gt;=0,C11*Вводные!$B$28,IF(Вводные!$B$30="Да",C11*Вводные!$B$28,C11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-86525.8613861387</v>
       </c>
       <c r="D22" s="49" t="n">
-        <f aca="false">IF(D11&gt;=0,D11*Вводные!$B$26,IF(Вводные!$B$28="Да",D11*Вводные!$B$26,D11))-MAX(0,IF(D11&gt;=0,D11*Вводные!$B$26,IF(Вводные!$B$28="Да",D11*Вводные!$B$26,D11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-30910.495049505</v>
+        <f aca="false">IF(D11&gt;=0,D11*Вводные!$B$28,IF(Вводные!$B$30="Да",D11*Вводные!$B$28,D11))-MAX(0,IF(D11&gt;=0,D11*Вводные!$B$28,IF(Вводные!$B$30="Да",D11*Вводные!$B$28,D11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-44027.3267326733</v>
       </c>
       <c r="E22" s="49" t="n">
-        <f aca="false">IF(E11&gt;=0,E11*Вводные!$B$26,IF(Вводные!$B$28="Да",E11*Вводные!$B$26,E11))-MAX(0,IF(E11&gt;=0,E11*Вводные!$B$26,IF(Вводные!$B$28="Да",E11*Вводные!$B$26,E11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>14211.405940594</v>
+        <f aca="false">IF(E11&gt;=0,E11*Вводные!$B$28,IF(Вводные!$B$30="Да",E11*Вводные!$B$28,E11))-MAX(0,IF(E11&gt;=0,E11*Вводные!$B$28,IF(Вводные!$B$30="Да",E11*Вводные!$B$28,E11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-1528.79207920798</v>
       </c>
       <c r="F22" s="49" t="n">
-        <f aca="false">IF(F11&gt;=0,F11*Вводные!$B$26,IF(Вводные!$B$28="Да",F11*Вводные!$B$26,F11))-MAX(0,IF(F11&gt;=0,F11*Вводные!$B$26,IF(Вводные!$B$28="Да",F11*Вводные!$B$26,F11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>59333.306930693</v>
+        <f aca="false">IF(F11&gt;=0,F11*Вводные!$B$28,IF(Вводные!$B$30="Да",F11*Вводные!$B$28,F11))-MAX(0,IF(F11&gt;=0,F11*Вводные!$B$28,IF(Вводные!$B$30="Да",F11*Вводные!$B$28,F11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>40969.7425742574</v>
       </c>
       <c r="G22" s="49" t="n">
-        <f aca="false">IF(G11&gt;=0,G11*Вводные!$B$26,IF(Вводные!$B$28="Да",G11*Вводные!$B$26,G11))-MAX(0,IF(G11&gt;=0,G11*Вводные!$B$26,IF(Вводные!$B$28="Да",G11*Вводные!$B$26,G11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>104455.207920792</v>
+        <f aca="false">IF(G11&gt;=0,G11*Вводные!$B$28,IF(Вводные!$B$30="Да",G11*Вводные!$B$28,G11))-MAX(0,IF(G11&gt;=0,G11*Вводные!$B$28,IF(Вводные!$B$30="Да",G11*Вводные!$B$28,G11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>83468.2772277227</v>
       </c>
       <c r="H22" s="49" t="n">
-        <f aca="false">IF(H11&gt;=0,H11*Вводные!$B$26,IF(Вводные!$B$28="Да",H11*Вводные!$B$26,H11))-MAX(0,IF(H11&gt;=0,H11*Вводные!$B$26,IF(Вводные!$B$28="Да",H11*Вводные!$B$26,H11)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>149577.108910891</v>
+        <f aca="false">IF(H11&gt;=0,H11*Вводные!$B$28,IF(Вводные!$B$30="Да",H11*Вводные!$B$28,H11))-MAX(0,IF(H11&gt;=0,H11*Вводные!$B$28,IF(Вводные!$B$30="Да",H11*Вводные!$B$28,H11)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>125966.811881188</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3423,32 +3473,32 @@
         <v>0.9</v>
       </c>
       <c r="B23" s="49" t="n">
-        <f aca="false">IF(B12&gt;=0,B12*Вводные!$B$26,IF(Вводные!$B$28="Да",B12*Вводные!$B$26,B12))-MAX(0,IF(B12&gt;=0,B12*Вводные!$B$26,IF(Вводные!$B$28="Да",B12*Вводные!$B$26,B12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-104233.584158416</v>
+        <f aca="false">IF(B12&gt;=0,B12*Вводные!$B$28,IF(Вводные!$B$30="Да",B12*Вводные!$B$28,B12))-MAX(0,IF(B12&gt;=0,B12*Вводные!$B$28,IF(Вводные!$B$30="Да",B12*Вводные!$B$28,B12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-113087.445544554</v>
       </c>
       <c r="C23" s="49" t="n">
-        <f aca="false">IF(C12&gt;=0,C12*Вводные!$B$26,IF(Вводные!$B$28="Да",C12*Вводные!$B$26,C12))-MAX(0,IF(C12&gt;=0,C12*Вводные!$B$26,IF(Вводные!$B$28="Да",C12*Вводные!$B$26,C12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-53471.4455445544</v>
+        <f aca="false">IF(C12&gt;=0,C12*Вводные!$B$28,IF(Вводные!$B$30="Да",C12*Вводные!$B$28,C12))-MAX(0,IF(C12&gt;=0,C12*Вводные!$B$28,IF(Вводные!$B$30="Да",C12*Вводные!$B$28,C12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-65276.594059406</v>
       </c>
       <c r="D23" s="49" t="n">
-        <f aca="false">IF(D12&gt;=0,D12*Вводные!$B$26,IF(Вводные!$B$28="Да",D12*Вводные!$B$26,D12))-MAX(0,IF(D12&gt;=0,D12*Вводные!$B$26,IF(Вводные!$B$28="Да",D12*Вводные!$B$26,D12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-2709.30693069307</v>
+        <f aca="false">IF(D12&gt;=0,D12*Вводные!$B$28,IF(Вводные!$B$30="Да",D12*Вводные!$B$28,D12))-MAX(0,IF(D12&gt;=0,D12*Вводные!$B$28,IF(Вводные!$B$30="Да",D12*Вводные!$B$28,D12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-17465.7425742574</v>
       </c>
       <c r="E23" s="49" t="n">
-        <f aca="false">IF(E12&gt;=0,E12*Вводные!$B$26,IF(Вводные!$B$28="Да",E12*Вводные!$B$26,E12))-MAX(0,IF(E12&gt;=0,E12*Вводные!$B$26,IF(Вводные!$B$28="Да",E12*Вводные!$B$26,E12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>48052.8316831683</v>
+        <f aca="false">IF(E12&gt;=0,E12*Вводные!$B$28,IF(Вводные!$B$30="Да",E12*Вводные!$B$28,E12))-MAX(0,IF(E12&gt;=0,E12*Вводные!$B$28,IF(Вводные!$B$30="Да",E12*Вводные!$B$28,E12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>30345.1089108911</v>
       </c>
       <c r="F23" s="49" t="n">
-        <f aca="false">IF(F12&gt;=0,F12*Вводные!$B$26,IF(Вводные!$B$28="Да",F12*Вводные!$B$26,F12))-MAX(0,IF(F12&gt;=0,F12*Вводные!$B$26,IF(Вводные!$B$28="Да",F12*Вводные!$B$26,F12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>98814.9702970297</v>
+        <f aca="false">IF(F12&gt;=0,F12*Вводные!$B$28,IF(Вводные!$B$30="Да",F12*Вводные!$B$28,F12))-MAX(0,IF(F12&gt;=0,F12*Вводные!$B$28,IF(Вводные!$B$30="Да",F12*Вводные!$B$28,F12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>78155.9603960396</v>
       </c>
       <c r="G23" s="49" t="n">
-        <f aca="false">IF(G12&gt;=0,G12*Вводные!$B$26,IF(Вводные!$B$28="Да",G12*Вводные!$B$26,G12))-MAX(0,IF(G12&gt;=0,G12*Вводные!$B$26,IF(Вводные!$B$28="Да",G12*Вводные!$B$26,G12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>149577.108910891</v>
+        <f aca="false">IF(G12&gt;=0,G12*Вводные!$B$28,IF(Вводные!$B$30="Да",G12*Вводные!$B$28,G12))-MAX(0,IF(G12&gt;=0,G12*Вводные!$B$28,IF(Вводные!$B$30="Да",G12*Вводные!$B$28,G12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>125966.811881188</v>
       </c>
       <c r="H23" s="49" t="n">
-        <f aca="false">IF(H12&gt;=0,H12*Вводные!$B$26,IF(Вводные!$B$28="Да",H12*Вводные!$B$26,H12))-MAX(0,IF(H12&gt;=0,H12*Вводные!$B$26,IF(Вводные!$B$28="Да",H12*Вводные!$B$26,H12)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>200339.247524753</v>
+        <f aca="false">IF(H12&gt;=0,H12*Вводные!$B$28,IF(Вводные!$B$30="Да",H12*Вводные!$B$28,H12))-MAX(0,IF(H12&gt;=0,H12*Вводные!$B$28,IF(Вводные!$B$30="Да",H12*Вводные!$B$28,H12)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>173777.663366337</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3456,32 +3506,32 @@
         <v>1</v>
       </c>
       <c r="B24" s="49" t="n">
-        <f aca="false">IF(B13&gt;=0,B13*Вводные!$B$26,IF(Вводные!$B$28="Да",B13*Вводные!$B$26,B13))-MAX(0,IF(B13&gt;=0,B13*Вводные!$B$26,IF(Вводные!$B$28="Да",B13*Вводные!$B$26,B13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-87312.8712871287</v>
+        <f aca="false">IF(B13&gt;=0,B13*Вводные!$B$28,IF(Вводные!$B$30="Да",B13*Вводные!$B$28,B13))-MAX(0,IF(B13&gt;=0,B13*Вводные!$B$28,IF(Вводные!$B$30="Да",B13*Вводные!$B$28,B13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-97150.495049505</v>
       </c>
       <c r="C24" s="49" t="n">
-        <f aca="false">IF(C13&gt;=0,C13*Вводные!$B$26,IF(Вводные!$B$28="Да",C13*Вводные!$B$26,C13))-MAX(0,IF(C13&gt;=0,C13*Вводные!$B$26,IF(Вводные!$B$28="Да",C13*Вводные!$B$26,C13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>-30910.495049505</v>
+        <f aca="false">IF(C13&gt;=0,C13*Вводные!$B$28,IF(Вводные!$B$30="Да",C13*Вводные!$B$28,C13))-MAX(0,IF(C13&gt;=0,C13*Вводные!$B$28,IF(Вводные!$B$30="Да",C13*Вводные!$B$28,C13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>-44027.3267326733</v>
       </c>
       <c r="D24" s="49" t="n">
-        <f aca="false">IF(D13&gt;=0,D13*Вводные!$B$26,IF(Вводные!$B$28="Да",D13*Вводные!$B$26,D13))-MAX(0,IF(D13&gt;=0,D13*Вводные!$B$26,IF(Вводные!$B$28="Да",D13*Вводные!$B$26,D13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>25491.8811881188</v>
+        <f aca="false">IF(D13&gt;=0,D13*Вводные!$B$28,IF(Вводные!$B$30="Да",D13*Вводные!$B$28,D13))-MAX(0,IF(D13&gt;=0,D13*Вводные!$B$28,IF(Вводные!$B$30="Да",D13*Вводные!$B$28,D13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>9095.84158415836</v>
       </c>
       <c r="E24" s="49" t="n">
-        <f aca="false">IF(E13&gt;=0,E13*Вводные!$B$26,IF(Вводные!$B$28="Да",E13*Вводные!$B$26,E13))-MAX(0,IF(E13&gt;=0,E13*Вводные!$B$26,IF(Вводные!$B$28="Да",E13*Вводные!$B$26,E13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>81894.2574257425</v>
+        <f aca="false">IF(E13&gt;=0,E13*Вводные!$B$28,IF(Вводные!$B$30="Да",E13*Вводные!$B$28,E13))-MAX(0,IF(E13&gt;=0,E13*Вводные!$B$28,IF(Вводные!$B$30="Да",E13*Вводные!$B$28,E13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>62219.00990099</v>
       </c>
       <c r="F24" s="49" t="n">
-        <f aca="false">IF(F13&gt;=0,F13*Вводные!$B$26,IF(Вводные!$B$28="Да",F13*Вводные!$B$26,F13))-MAX(0,IF(F13&gt;=0,F13*Вводные!$B$26,IF(Вводные!$B$28="Да",F13*Вводные!$B$26,F13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>138296.633663366</v>
+        <f aca="false">IF(F13&gt;=0,F13*Вводные!$B$28,IF(Вводные!$B$30="Да",F13*Вводные!$B$28,F13))-MAX(0,IF(F13&gt;=0,F13*Вводные!$B$28,IF(Вводные!$B$30="Да",F13*Вводные!$B$28,F13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>115342.178217822</v>
       </c>
       <c r="G24" s="49" t="n">
-        <f aca="false">IF(G13&gt;=0,G13*Вводные!$B$26,IF(Вводные!$B$28="Да",G13*Вводные!$B$26,G13))-MAX(0,IF(G13&gt;=0,G13*Вводные!$B$26,IF(Вводные!$B$28="Да",G13*Вводные!$B$26,G13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>194699.00990099</v>
+        <f aca="false">IF(G13&gt;=0,G13*Вводные!$B$28,IF(Вводные!$B$30="Да",G13*Вводные!$B$28,G13))-MAX(0,IF(G13&gt;=0,G13*Вводные!$B$28,IF(Вводные!$B$30="Да",G13*Вводные!$B$28,G13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>168465.346534653</v>
       </c>
       <c r="H24" s="49" t="n">
-        <f aca="false">IF(H13&gt;=0,H13*Вводные!$B$26,IF(Вводные!$B$28="Да",H13*Вводные!$B$26,H13))-MAX(0,IF(H13&gt;=0,H13*Вводные!$B$26,IF(Вводные!$B$28="Да",H13*Вводные!$B$26,H13)))*Вводные!$B$33-Экономика!$C$76</f>
-        <v>251101.386138614</v>
+        <f aca="false">IF(H13&gt;=0,H13*Вводные!$B$28,IF(Вводные!$B$30="Да",H13*Вводные!$B$28,H13))-MAX(0,IF(H13&gt;=0,H13*Вводные!$B$28,IF(Вводные!$B$30="Да",H13*Вводные!$B$28,H13)))*Вводные!$B$35-Экономика!$C$76</f>
+        <v>221588.514851485</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3506,7 +3556,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="89" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -3518,7 +3568,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="92" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B28" s="90" t="n">
         <v>1500</v>
@@ -3544,68 +3594,68 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/B$28,0),"н/д")</f>
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="C29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/C$28,0),"н/д")</f>
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="D29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/D$28,0),"н/д")</f>
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="E29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/E$28,0),"н/д")</f>
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/F$28,0),"н/д")</f>
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/G$28,0),"н/д")</f>
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H29" s="93" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/H$28,0),"н/д")</f>
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B30" s="94" t="n">
         <f aca="false">IFERROR(B29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>1.51850694444444</v>
+        <v>1.6096875</v>
       </c>
       <c r="C30" s="94" t="n">
         <f aca="false">IFERROR(C29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>1.13975694444444</v>
+        <v>1.20989583333333</v>
       </c>
       <c r="D30" s="94" t="n">
         <f aca="false">IFERROR(D29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>0.911805555555556</v>
+        <v>0.967916666666667</v>
       </c>
       <c r="E30" s="94" t="n">
         <f aca="false">IFERROR(E29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>0.761006944444445</v>
+        <v>0.806597222222222</v>
       </c>
       <c r="F30" s="94" t="n">
         <f aca="false">IFERROR(F29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>0.652291666666667</v>
+        <v>0.690868055555556</v>
       </c>
       <c r="G30" s="94" t="n">
         <f aca="false">IFERROR(G29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>0.571631944444444</v>
+        <v>0.606701388888889</v>
       </c>
       <c r="H30" s="94" t="n">
         <f aca="false">IFERROR(H29/Билеты!$B$22/Вводные!$B$12,"н/д")</f>
-        <v>0.508506944444444</v>
+        <v>0.5365625</v>
       </c>
     </row>
   </sheetData>
@@ -3666,7 +3716,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3678,7 +3728,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3700,22 +3750,22 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -3725,19 +3775,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="96" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C5" s="97" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D5" s="98" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E5" s="99" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F5" s="100" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -3747,19 +3797,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="96" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C6" s="97" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E6" s="99" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F6" s="100" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3769,19 +3819,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="96" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C7" s="97" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D7" s="98" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E7" s="99" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F7" s="100" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -3791,19 +3841,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="102" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C8" s="103" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D8" s="104" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E8" s="105" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F8" s="106" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -3813,19 +3863,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="108" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D9" s="110" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E9" s="111" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F9" s="112" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -3835,19 +3885,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="102" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C10" s="103" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D10" s="104" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E10" s="105" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="F10" s="106" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -3857,19 +3907,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="108" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C11" s="109" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D11" s="110" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E11" s="111" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F11" s="112" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -3879,19 +3929,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="102" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C12" s="103" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D12" s="104" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E12" s="105" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F12" s="106" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -3901,19 +3951,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C13" s="109" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D13" s="110" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E13" s="111" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F13" s="112" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -3923,19 +3973,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="102" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C14" s="103" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D14" s="104" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E14" s="105" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="F14" s="106" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -3945,19 +3995,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="108" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C15" s="109" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D15" s="110" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E15" s="111" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F15" s="112" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -3967,19 +4017,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="102" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C16" s="103" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D16" s="104" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E16" s="105" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F16" s="106" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -3989,19 +4039,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="108" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C17" s="109" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D17" s="110" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E17" s="111" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F17" s="112" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -4011,19 +4061,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="102" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C18" s="103" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E18" s="105" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F18" s="106" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -4033,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="108" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D19" s="110" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E19" s="111" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F19" s="112" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -4055,19 +4105,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="102" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C20" s="103" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D20" s="104" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E20" s="105" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="F20" s="106" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -4088,7 +4138,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
@@ -4098,7 +4148,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4110,7 +4160,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4132,7 +4182,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4144,10 +4194,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -4158,10 +4208,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -4172,10 +4222,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -4186,10 +4236,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -4200,10 +4250,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -4224,7 +4274,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -4236,7 +4286,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>300</v>
@@ -4250,13 +4300,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B13" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -4266,7 +4316,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" s="25" t="n">
         <v>0.9</v>
@@ -4280,7 +4330,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
@@ -4304,7 +4354,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -4316,13 +4366,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="25" t="n">
         <v>0.06</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -4332,13 +4382,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B19" s="25" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -4347,88 +4397,94 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="A20" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="27" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="27" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="25" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -4436,31 +4492,26 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="28" t="n">
-        <f aca="false">1-Вводные!$B$26</f>
-        <v>0.5</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>76</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -4468,8 +4519,13 @@
       <c r="H28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+      <c r="A29" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="28" t="n">
+        <f aca="false">1-Вводные!$B$28</f>
+        <v>0.5</v>
+      </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -4477,57 +4533,54 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="25" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="25" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="30" t="n">
-        <f aca="false">Вводные!$B$31+Вводные!$B$32</f>
-        <v>0.08</v>
-      </c>
-      <c r="C33" s="4"/>
+      <c r="A33" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -4535,8 +4588,12 @@
       <c r="H33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
+      <c r="A34" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>0.01</v>
+      </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -4544,52 +4601,49 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="30" t="n">
+        <f aca="false">Вводные!$B$33+Вводные!$B$34</f>
+        <v>0.08</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="4"/>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -4598,10 +4652,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -4611,8 +4665,12 @@
       <c r="H39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4620,25 +4678,23 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -4646,20 +4702,50 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A38:C38"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B22" type="list">
+  <dataValidations count="4">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B20" type="list">
+      <formula1>"Валовой сбор,Сбор после вычета УСН"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B24" type="list">
       <formula1>"Из сметы,Фиксированной суммой"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B28" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B30" type="list">
       <formula1>"Да,Нет"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B37:B39" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B39:B41" type="list">
       <formula1>"Да,Нет"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4695,7 +4781,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4707,7 +4793,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4729,7 +4815,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4741,33 +4827,33 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B6" s="27" t="n">
         <v>1800</v>
@@ -4791,12 +4877,12 @@
         <v>0.220124436816134</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="27" t="n">
         <v>2500</v>
@@ -4820,12 +4906,12 @@
         <v>0.482729028105557</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>2800</v>
@@ -4849,12 +4935,12 @@
         <v>0.120145891439605</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>4000</v>
@@ -4878,12 +4964,12 @@
         <v>0.154473288993778</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B10" s="27" t="n">
         <v>1500</v>
@@ -4907,12 +4993,12 @@
         <v>0.022527354644926</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B11" s="27" t="n">
         <v>0</v>
@@ -4936,12 +5022,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40" t="n">
@@ -4975,7 +5061,7 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -4987,7 +5073,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B15" s="43" t="str">
         <f aca="false">IF(Билеты!$C$12=Вводные!$B$12,"OK — квоты сходятся с залом","ВНИМАНИЕ: квоты ("&amp;Билеты!$C$12&amp;") ≠ вместимость ("&amp;Вводные!$B$12&amp;")")</f>
@@ -5002,7 +5088,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B16" s="44" t="n">
         <f aca="false">Билеты!$E$12</f>
@@ -5017,7 +5103,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B17" s="45" t="n">
         <f aca="false">SUMIF(B6:B11,"&gt;0",E6:E11)</f>
@@ -5032,7 +5118,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B18" s="46" t="n">
         <f aca="false">Билеты!$F$12</f>
@@ -5047,7 +5133,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B19" s="47" t="n">
         <f aca="false">IFERROR(Билеты!$F$12/Билеты!$B$17,0)</f>
@@ -5062,7 +5148,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B20" s="47" t="n">
         <f aca="false">IFERROR(Билеты!$F$12/Вводные!$B$12,0)</f>
@@ -5077,7 +5163,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">IFERROR(Билеты!$E$12/Вводные!$B$12,0)</f>
@@ -5092,7 +5178,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">IFERROR(Билеты!$B$17/Билеты!$E$12,0)</f>
@@ -5133,7 +5219,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5143,7 +5229,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -5161,33 +5247,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>20000</v>
@@ -5197,18 +5283,18 @@
         <v>20000</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D6" s="27" t="n">
         <v>25000</v>
@@ -5218,18 +5304,18 @@
         <v>25000</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>8000</v>
@@ -5239,18 +5325,18 @@
         <v>8000</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D8" s="27" t="n">
         <v>10000</v>
@@ -5260,18 +5346,18 @@
         <v>10000</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>15000</v>
@@ -5281,18 +5367,18 @@
         <v>15000</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B10" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D10" s="27" t="n">
         <v>12000</v>
@@ -5302,18 +5388,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B11" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>15000</v>
@@ -5326,13 +5412,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D12" s="27" t="n">
         <v>8000</v>
@@ -5342,18 +5428,18 @@
         <v>8000</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>20000</v>
@@ -5363,18 +5449,18 @@
         <v>0</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B14" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D14" s="27" t="n">
         <v>18000</v>
@@ -5384,18 +5470,18 @@
         <v>0</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B15" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D15" s="27" t="n">
         <v>3000</v>
@@ -5408,13 +5494,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B16" s="24" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D16" s="27" t="n">
         <v>3500</v>
@@ -5424,18 +5510,18 @@
         <v>10500</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B17" s="24" t="n">
         <v>3</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>4000</v>
@@ -5445,18 +5531,18 @@
         <v>12000</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>3</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>3000</v>
@@ -5469,13 +5555,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>3000</v>
@@ -5488,13 +5574,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D20" s="27" t="n">
         <v>5000</v>
@@ -5504,18 +5590,18 @@
         <v>5000</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>8000</v>
@@ -5528,7 +5614,7 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
@@ -5567,7 +5653,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5577,7 +5663,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -5595,33 +5681,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>25000</v>
@@ -5631,18 +5717,18 @@
         <v>25000</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D6" s="27" t="n">
         <v>8000</v>
@@ -5655,13 +5741,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>8000</v>
@@ -5674,13 +5760,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D8" s="27" t="n">
         <v>8000</v>
@@ -5693,13 +5779,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>8000</v>
@@ -5709,18 +5795,18 @@
         <v>0</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B10" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D10" s="27" t="n">
         <v>10000</v>
@@ -5730,18 +5816,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B11" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>8000</v>
@@ -5754,13 +5840,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D12" s="27" t="n">
         <v>15000</v>
@@ -5770,12 +5856,12 @@
         <v>0</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B13" s="51"/>
       <c r="C13" s="51"/>
@@ -5802,7 +5888,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5814,7 +5900,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5824,7 +5910,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -5842,115 +5928,113 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B5" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>40000</v>
+        <v>12000</v>
       </c>
       <c r="E5" s="49" t="n">
         <f aca="false">B5*D5</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="49" t="n">
         <f aca="false">B6*D6</f>
-        <v>12000</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>182</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="F6" s="37"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B7" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="E7" s="49" t="n">
         <f aca="false">B7*D7</f>
-        <v>5000</v>
-      </c>
-      <c r="F7" s="37"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B8" s="24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="E8" s="49" t="n">
         <f aca="false">B8*D8</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>185</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="F8" s="37"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>6000</v>
@@ -5959,203 +6043,184 @@
         <f aca="false">B9*D9</f>
         <v>12000</v>
       </c>
-      <c r="F9" s="37"/>
+      <c r="F9" s="37" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B10" s="24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="E10" s="49" t="n">
         <f aca="false">B10*D10</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B11" s="24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>25000</v>
+        <v>700</v>
       </c>
       <c r="E11" s="49" t="n">
         <f aca="false">B11*D11</f>
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B12" s="24" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>700</v>
+        <v>12000</v>
       </c>
       <c r="E12" s="49" t="n">
         <f aca="false">B12*D12</f>
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B13" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="E13" s="49" t="n">
         <f aca="false">B13*D13</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B14" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="E14" s="49" t="n">
         <f aca="false">B14*D14</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B15" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="E15" s="49" t="n">
         <f aca="false">B15*D15</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B16" s="24" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D16" s="27" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="E16" s="49" t="n">
         <f aca="false">B16*D16</f>
         <v>0</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="B17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="27" t="n">
-        <v>12000</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
       <c r="E17" s="49" t="n">
-        <f aca="false">B17*D17</f>
-        <v>0</v>
+        <f aca="false">SUM(E5:E16)*Вводные!$B$44</f>
+        <v>6950</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="49" t="n">
-        <f aca="false">SUM(E5:E17)*Вводные!$B$42</f>
-        <v>6950</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="52" t="n">
-        <f aca="false">SUM(E5:E18)</f>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="52" t="n">
+        <f aca="false">SUM(E5:E17)</f>
         <v>76450</v>
       </c>
-      <c r="F19" s="51"/>
+      <c r="F18" s="51"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6188,7 +6253,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6200,7 +6265,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -6222,7 +6287,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -6234,33 +6299,33 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B6" s="27" t="n">
         <v>20000</v>
@@ -6283,12 +6348,12 @@
         <v>465.116279069767</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B7" s="27" t="n">
         <v>15000</v>
@@ -6311,12 +6376,12 @@
         <v>340.909090909091</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>10000</v>
@@ -6339,12 +6404,12 @@
         <v>322.58064516129</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>5000</v>
@@ -6367,12 +6432,12 @@
         <v>1000</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B10" s="27" t="n">
         <v>0</v>
@@ -6395,12 +6460,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B11" s="27" t="n">
         <v>3000</v>
@@ -6423,12 +6488,12 @@
         <v>600</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B12" s="27" t="n">
         <v>1000</v>
@@ -6451,12 +6516,12 @@
         <v>17.2413793103448</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>6000</v>
@@ -6479,12 +6544,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="50" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B14" s="52" t="n">
         <f aca="false">SUM(B6:B13)</f>
@@ -6518,7 +6583,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -6530,7 +6595,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B17" s="46" t="n">
         <f aca="false">Маркетинг!$B$14</f>
@@ -6545,7 +6610,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B18" s="44" t="n">
         <f aca="false">Маркетинг!$F$14</f>
@@ -6560,7 +6625,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B19" s="44" t="n">
         <f aca="false">Билеты!$B$17</f>
@@ -6575,14 +6640,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B20" s="28" t="n">
         <f aca="false">IFERROR(Маркетинг!$F$14/Билеты!$B$17,0)</f>
         <v>1.02083333333333</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -6592,14 +6657,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">IFERROR(Маркетинг!$G$14/Билеты!$B$19,0)</f>
         <v>0.126100644076554</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -6609,14 +6674,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">IFERROR(Маркетинг!$B$14/Билеты!$F$12,0)</f>
         <v>0.128727740828148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -6626,7 +6691,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B23" s="43" t="str">
         <f aca="false">IF(Маркетинг!$B$22&gt;0.2,"ПЕРЕРАСХОД: маркетинг забирает больше 20% сбора",IF(Маркетинг!$B$20&lt;1,"РИСК: маркетинг не покрывает план продаж","Норма: бюджет и план продаж сбалансированы"))</f>
@@ -6672,7 +6737,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6684,7 +6749,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -6706,19 +6771,19 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -6726,7 +6791,7 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -6738,7 +6803,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="56" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="57" t="n">
@@ -6750,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -6758,7 +6823,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="60" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B7" s="53"/>
       <c r="C7" s="47" t="n">
@@ -6770,7 +6835,7 @@
         <v>-0.06</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -6778,68 +6843,72 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B8" s="53"/>
       <c r="C8" s="47" t="n">
-        <f aca="false">-Экономика!$C$6*Вводные!$B$19</f>
-        <v>-37288</v>
+        <f aca="false">-IF(Вводные!$B$20="Валовой сбор",Билеты!$F$12,Билеты!$F$12*(1-Вводные!$B$18))*Вводные!$B$19</f>
+        <v>-23305</v>
       </c>
       <c r="D8" s="21" t="n">
         <f aca="false">IFERROR(C8/$C$6,0)</f>
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="61" t="s">
-        <v>258</v>
+      <c r="A9" s="60" t="s">
+        <v>262</v>
       </c>
       <c r="B9" s="53"/>
-      <c r="C9" s="62" t="n">
-        <f aca="false">-IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)</f>
-        <v>-154500</v>
+      <c r="C9" s="47" t="n">
+        <f aca="false">-Экономика!$C$6*Вводные!$B$21</f>
+        <v>-37288</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">IFERROR(C9/$C$6,0)</f>
-        <v>-0.331473932632482</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A10" s="63" t="str">
-        <f aca="false">Технические!$A$5</f>
-        <v>Аренда зала (смена)</v>
-      </c>
-      <c r="B10" s="64" t="n">
-        <f aca="false">-Технические!$E$5</f>
-        <v>-20000</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="53"/>
+      <c r="C10" s="62" t="n">
+        <f aca="false">-IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)</f>
+        <v>-154500</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <f aca="false">IFERROR(C10/$C$6,0)</f>
+        <v>-0.331473932632482</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>265</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A11" s="63" t="str">
-        <f aca="false">Технические!$A$6</f>
-        <v>Аренда звукового комплекта PA</v>
+        <f aca="false">Технические!$A$5</f>
+        <v>Аренда зала (смена)</v>
       </c>
       <c r="B11" s="64" t="n">
-        <f aca="false">-Технические!$E$6</f>
-        <v>-25000</v>
+        <f aca="false">-Технические!$E$5</f>
+        <v>-20000</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="65"/>
@@ -6850,12 +6919,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A12" s="63" t="str">
-        <f aca="false">Технические!$A$7</f>
-        <v>Микрофоны, радиосистемы, стойки</v>
+        <f aca="false">Технические!$A$6</f>
+        <v>Аренда звукового комплекта PA</v>
       </c>
       <c r="B12" s="64" t="n">
-        <f aca="false">-Технические!$E$7</f>
-        <v>-8000</v>
+        <f aca="false">-Технические!$E$6</f>
+        <v>-25000</v>
       </c>
       <c r="C12" s="65"/>
       <c r="D12" s="65"/>
@@ -6866,12 +6935,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A13" s="63" t="str">
-        <f aca="false">Технические!$A$8</f>
-        <v>Мониторная линия / in-ear</v>
+        <f aca="false">Технические!$A$7</f>
+        <v>Микрофоны, радиосистемы, стойки</v>
       </c>
       <c r="B13" s="64" t="n">
-        <f aca="false">-Технические!$E$8</f>
-        <v>-10000</v>
+        <f aca="false">-Технические!$E$7</f>
+        <v>-8000</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="65"/>
@@ -6882,12 +6951,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A14" s="63" t="str">
-        <f aca="false">Технические!$A$9</f>
-        <v>Звукорежиссёр FOH</v>
+        <f aca="false">Технические!$A$8</f>
+        <v>Мониторная линия / in-ear</v>
       </c>
       <c r="B14" s="64" t="n">
-        <f aca="false">-Технические!$E$9</f>
-        <v>-15000</v>
+        <f aca="false">-Технические!$E$8</f>
+        <v>-10000</v>
       </c>
       <c r="C14" s="65"/>
       <c r="D14" s="65"/>
@@ -6898,12 +6967,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A15" s="63" t="str">
-        <f aca="false">Технические!$A$10</f>
-        <v>Мониторный инженер</v>
+        <f aca="false">Технические!$A$9</f>
+        <v>Звукорежиссёр FOH</v>
       </c>
       <c r="B15" s="64" t="n">
-        <f aca="false">-Технические!$E$10</f>
-        <v>-0</v>
+        <f aca="false">-Технические!$E$9</f>
+        <v>-15000</v>
       </c>
       <c r="C15" s="65"/>
       <c r="D15" s="65"/>
@@ -6914,12 +6983,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A16" s="63" t="str">
-        <f aca="false">Технические!$A$11</f>
-        <v>Световое оборудование</v>
+        <f aca="false">Технические!$A$10</f>
+        <v>Мониторный инженер</v>
       </c>
       <c r="B16" s="64" t="n">
-        <f aca="false">-Технические!$E$11</f>
-        <v>-15000</v>
+        <f aca="false">-Технические!$E$10</f>
+        <v>-0</v>
       </c>
       <c r="C16" s="65"/>
       <c r="D16" s="65"/>
@@ -6930,12 +6999,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A17" s="63" t="str">
-        <f aca="false">Технические!$A$12</f>
-        <v>Художник по свету / оператор</v>
+        <f aca="false">Технические!$A$11</f>
+        <v>Световое оборудование</v>
       </c>
       <c r="B17" s="64" t="n">
-        <f aca="false">-Технические!$E$12</f>
-        <v>-8000</v>
+        <f aca="false">-Технические!$E$11</f>
+        <v>-15000</v>
       </c>
       <c r="C17" s="65"/>
       <c r="D17" s="65"/>
@@ -6946,12 +7015,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A18" s="63" t="str">
-        <f aca="false">Технические!$A$13</f>
-        <v>Бэклайн: барабаны, усилители, клавиши</v>
+        <f aca="false">Технические!$A$12</f>
+        <v>Художник по свету / оператор</v>
       </c>
       <c r="B18" s="64" t="n">
-        <f aca="false">-Технические!$E$13</f>
-        <v>-0</v>
+        <f aca="false">-Технические!$E$12</f>
+        <v>-8000</v>
       </c>
       <c r="C18" s="65"/>
       <c r="D18" s="65"/>
@@ -6962,11 +7031,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A19" s="63" t="str">
-        <f aca="false">Технические!$A$14</f>
-        <v>Экран, проекция, видеоконтент</v>
+        <f aca="false">Технические!$A$13</f>
+        <v>Бэклайн: барабаны, усилители, клавиши</v>
       </c>
       <c r="B19" s="64" t="n">
-        <f aca="false">-Технические!$E$14</f>
+        <f aca="false">-Технические!$E$13</f>
         <v>-0</v>
       </c>
       <c r="C19" s="65"/>
@@ -6978,12 +7047,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A20" s="63" t="str">
-        <f aca="false">Технические!$A$15</f>
-        <v>Электрика, кабели, распределение</v>
+        <f aca="false">Технические!$A$14</f>
+        <v>Экран, проекция, видеоконтент</v>
       </c>
       <c r="B20" s="64" t="n">
-        <f aca="false">-Технические!$E$15</f>
-        <v>-3000</v>
+        <f aca="false">-Технические!$E$14</f>
+        <v>-0</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
@@ -6994,12 +7063,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A21" s="63" t="str">
-        <f aca="false">Технические!$A$16</f>
-        <v>Монтаж, демонтаж, погрузка</v>
+        <f aca="false">Технические!$A$15</f>
+        <v>Электрика, кабели, распределение</v>
       </c>
       <c r="B21" s="64" t="n">
-        <f aca="false">-Технические!$E$16</f>
-        <v>-10500</v>
+        <f aca="false">-Технические!$E$15</f>
+        <v>-3000</v>
       </c>
       <c r="C21" s="65"/>
       <c r="D21" s="65"/>
@@ -7010,12 +7079,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A22" s="63" t="str">
-        <f aca="false">Технические!$A$17</f>
-        <v>Охрана</v>
+        <f aca="false">Технические!$A$16</f>
+        <v>Монтаж, демонтаж, погрузка</v>
       </c>
       <c r="B22" s="64" t="n">
-        <f aca="false">-Технические!$E$17</f>
-        <v>-12000</v>
+        <f aca="false">-Технические!$E$16</f>
+        <v>-10500</v>
       </c>
       <c r="C22" s="65"/>
       <c r="D22" s="65"/>
@@ -7026,12 +7095,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A23" s="63" t="str">
-        <f aca="false">Технические!$A$18</f>
-        <v>Билетный контроль и гардероб</v>
+        <f aca="false">Технические!$A$17</f>
+        <v>Охрана</v>
       </c>
       <c r="B23" s="64" t="n">
-        <f aca="false">-Технические!$E$18</f>
-        <v>-9000</v>
+        <f aca="false">-Технические!$E$17</f>
+        <v>-12000</v>
       </c>
       <c r="C23" s="65"/>
       <c r="D23" s="65"/>
@@ -7042,12 +7111,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A24" s="63" t="str">
-        <f aca="false">Технические!$A$19</f>
-        <v>Уборка до и после</v>
+        <f aca="false">Технические!$A$18</f>
+        <v>Билетный контроль и гардероб</v>
       </c>
       <c r="B24" s="64" t="n">
-        <f aca="false">-Технические!$E$19</f>
-        <v>-6000</v>
+        <f aca="false">-Технические!$E$18</f>
+        <v>-9000</v>
       </c>
       <c r="C24" s="65"/>
       <c r="D24" s="65"/>
@@ -7058,12 +7127,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A25" s="63" t="str">
-        <f aca="false">Технические!$A$20</f>
-        <v>Дежурный медик</v>
+        <f aca="false">Технические!$A$19</f>
+        <v>Уборка до и после</v>
       </c>
       <c r="B25" s="64" t="n">
-        <f aca="false">-Технические!$E$20</f>
-        <v>-5000</v>
+        <f aca="false">-Технические!$E$19</f>
+        <v>-6000</v>
       </c>
       <c r="C25" s="65"/>
       <c r="D25" s="65"/>
@@ -7074,12 +7143,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A26" s="63" t="str">
-        <f aca="false">Технические!$A$21</f>
-        <v>Администратор площадки</v>
+        <f aca="false">Технические!$A$20</f>
+        <v>Дежурный медик</v>
       </c>
       <c r="B26" s="64" t="n">
-        <f aca="false">-Технические!$E$21</f>
-        <v>-8000</v>
+        <f aca="false">-Технические!$E$20</f>
+        <v>-5000</v>
       </c>
       <c r="C26" s="65"/>
       <c r="D26" s="65"/>
@@ -7088,51 +7157,49 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="47" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Да",Гонорары!$E$13,0)</f>
-        <v>-0</v>
-      </c>
-      <c r="D27" s="21" t="n">
-        <f aca="false">IFERROR(C27/$C$6,0)</f>
-        <v>-0</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>261</v>
-      </c>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A27" s="63" t="str">
+        <f aca="false">Технические!$A$21</f>
+        <v>Администратор площадки</v>
+      </c>
+      <c r="B27" s="64" t="n">
+        <f aca="false">-Технические!$E$21</f>
+        <v>-8000</v>
+      </c>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="60" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B28" s="53"/>
       <c r="C28" s="47" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)</f>
+        <f aca="false">-IF(Вводные!$B$39="Да",Гонорары!$E$13,0)</f>
         <v>-0</v>
       </c>
       <c r="D28" s="21" t="n">
         <f aca="false">IFERROR(C28/$C$6,0)</f>
         <v>-0</v>
       </c>
-      <c r="E28" s="53"/>
+      <c r="E28" s="37" t="s">
+        <v>267</v>
+      </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="60" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B29" s="53"/>
       <c r="C29" s="47" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Да",Прочие!$E$19,0)</f>
+        <f aca="false">-IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)</f>
         <v>-0</v>
       </c>
       <c r="D29" s="21" t="n">
@@ -7144,188 +7211,190 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="66" t="s">
-        <v>264</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="67" t="n">
-        <f aca="false">Экономика!$C$6+Экономика!$C$7+Экономика!$C$8+Экономика!$C$9+Экономика!$C$27+Экономика!$C$28+Экономика!$C$29</f>
-        <v>246346</v>
-      </c>
-      <c r="D30" s="58" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="60" t="s">
+        <v>269</v>
+      </c>
+      <c r="B30" s="53"/>
+      <c r="C30" s="47" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Да",Прочие!$E$18,0)</f>
+        <v>-0</v>
+      </c>
+      <c r="D30" s="21" t="n">
         <f aca="false">IFERROR(C30/$C$6,0)</f>
-        <v>0.528526067367518</v>
-      </c>
-      <c r="E30" s="39"/>
+        <v>-0</v>
+      </c>
+      <c r="E30" s="53"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="67" t="n">
+        <f aca="false">Экономика!$C$6+Экономика!$C$7+Экономика!$C$8+Экономика!$C$9+Экономика!$C$10+Экономика!$C$28+Экономика!$C$29+Экономика!$C$30</f>
+        <v>223041</v>
+      </c>
+      <c r="D31" s="58" t="n">
+        <f aca="false">IFERROR(C31/$C$6,0)</f>
+        <v>0.478526067367518</v>
+      </c>
+      <c r="E31" s="39"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="47" t="n">
-        <f aca="false">-IF(Экономика!$C$30&gt;=0,Экономика!$C$30*Вводные!$B$27,IF(Вводные!$B$28="Да",Экономика!$C$30*Вводные!$B$27,0))</f>
-        <v>-123173</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <f aca="false">IFERROR(C33/$C$6,0)</f>
-        <v>-0.264263033683759</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>267</v>
-      </c>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="68" t="s">
-        <v>268</v>
-      </c>
-      <c r="B34" s="69"/>
-      <c r="C34" s="70" t="n">
-        <f aca="false">Экономика!$C$30+Экономика!$C$33</f>
-        <v>123173</v>
-      </c>
-      <c r="D34" s="71" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="B34" s="53"/>
+      <c r="C34" s="47" t="n">
+        <f aca="false">-IF(Экономика!$C$31&gt;=0,Экономика!$C$31*Вводные!$B$29,IF(Вводные!$B$30="Да",Экономика!$C$31*Вводные!$B$29,0))</f>
+        <v>-111520.5</v>
+      </c>
+      <c r="D34" s="21" t="n">
         <f aca="false">IFERROR(C34/$C$6,0)</f>
-        <v>0.264263033683759</v>
-      </c>
-      <c r="E34" s="72" t="s">
-        <v>269</v>
+        <v>-0.239263033683759</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>273</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" s="69"/>
+      <c r="C35" s="70" t="n">
+        <f aca="false">Экономика!$C$31+Экономика!$C$34</f>
+        <v>111520.5</v>
+      </c>
+      <c r="D35" s="71" t="n">
+        <f aca="false">IFERROR(C35/$C$6,0)</f>
+        <v>0.239263033683759</v>
+      </c>
+      <c r="E35" s="72" t="s">
+        <v>275</v>
+      </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="47" t="n">
-        <f aca="false">-MAX(0,Экономика!$C$34)*Вводные!$B$31</f>
-        <v>-8622.11</v>
-      </c>
-      <c r="D37" s="21" t="n">
-        <f aca="false">IFERROR(C37/$C$6,0)</f>
-        <v>-0.0184984123578631</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>270</v>
-      </c>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38" s="53"/>
       <c r="C38" s="47" t="n">
-        <f aca="false">-MAX(0,Экономика!$C$34)*Вводные!$B$32</f>
-        <v>-1231.73</v>
+        <f aca="false">-MAX(0,Экономика!$C$35)*Вводные!$B$33</f>
+        <v>-7806.435</v>
       </c>
       <c r="D38" s="21" t="n">
         <f aca="false">IFERROR(C38/$C$6,0)</f>
-        <v>-0.00264263033683759</v>
-      </c>
-      <c r="E38" s="53"/>
+        <v>-0.0167484123578631</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>276</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="61" t="s">
-        <v>16</v>
+      <c r="A39" s="60" t="s">
+        <v>17</v>
       </c>
       <c r="B39" s="53"/>
-      <c r="C39" s="62" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)</f>
-        <v>-49000</v>
+      <c r="C39" s="47" t="n">
+        <f aca="false">-MAX(0,Экономика!$C$35)*Вводные!$B$34</f>
+        <v>-1115.205</v>
       </c>
       <c r="D39" s="21" t="n">
         <f aca="false">IFERROR(C39/$C$6,0)</f>
-        <v>-0.105127655009655</v>
+        <v>-0.00239263033683759</v>
       </c>
       <c r="E39" s="53"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A40" s="63" t="str">
-        <f aca="false">Гонорары!$A$5</f>
-        <v>Артист / хедлайнер</v>
-      </c>
-      <c r="B40" s="64" t="n">
-        <f aca="false">-Гонорары!$E$5</f>
-        <v>-25000</v>
-      </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="53"/>
+      <c r="C40" s="62" t="n">
+        <f aca="false">-IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)</f>
+        <v>-49000</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <f aca="false">IFERROR(C40/$C$6,0)</f>
+        <v>-0.105127655009655</v>
+      </c>
+      <c r="E40" s="53"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A41" s="63" t="str">
-        <f aca="false">Гонорары!$A$6</f>
-        <v>Музыкант: гитара</v>
+        <f aca="false">Гонорары!$A$5</f>
+        <v>Артист / хедлайнер</v>
       </c>
       <c r="B41" s="64" t="n">
-        <f aca="false">-Гонорары!$E$6</f>
-        <v>-8000</v>
+        <f aca="false">-Гонорары!$E$5</f>
+        <v>-25000</v>
       </c>
       <c r="C41" s="65"/>
       <c r="D41" s="65"/>
@@ -7336,11 +7405,11 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A42" s="63" t="str">
-        <f aca="false">Гонорары!$A$7</f>
-        <v>Музыкант: бас</v>
+        <f aca="false">Гонорары!$A$6</f>
+        <v>Музыкант: гитара</v>
       </c>
       <c r="B42" s="64" t="n">
-        <f aca="false">-Гонорары!$E$7</f>
+        <f aca="false">-Гонорары!$E$6</f>
         <v>-8000</v>
       </c>
       <c r="C42" s="65"/>
@@ -7352,11 +7421,11 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A43" s="63" t="str">
-        <f aca="false">Гонорары!$A$8</f>
-        <v>Музыкант: барабаны</v>
+        <f aca="false">Гонорары!$A$7</f>
+        <v>Музыкант: бас</v>
       </c>
       <c r="B43" s="64" t="n">
-        <f aca="false">-Гонорары!$E$8</f>
+        <f aca="false">-Гонорары!$E$7</f>
         <v>-8000</v>
       </c>
       <c r="C43" s="65"/>
@@ -7368,12 +7437,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A44" s="63" t="str">
-        <f aca="false">Гонорары!$A$9</f>
-        <v>Музыкант: клавиши</v>
+        <f aca="false">Гонорары!$A$8</f>
+        <v>Музыкант: барабаны</v>
       </c>
       <c r="B44" s="64" t="n">
-        <f aca="false">-Гонорары!$E$9</f>
-        <v>-0</v>
+        <f aca="false">-Гонорары!$E$8</f>
+        <v>-8000</v>
       </c>
       <c r="C44" s="65"/>
       <c r="D44" s="65"/>
@@ -7384,11 +7453,11 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A45" s="63" t="str">
-        <f aca="false">Гонорары!$A$10</f>
-        <v>Разогрев / support act</v>
+        <f aca="false">Гонорары!$A$9</f>
+        <v>Музыкант: клавиши</v>
       </c>
       <c r="B45" s="64" t="n">
-        <f aca="false">-Гонорары!$E$10</f>
+        <f aca="false">-Гонорары!$E$9</f>
         <v>-0</v>
       </c>
       <c r="C45" s="65"/>
@@ -7400,11 +7469,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A46" s="63" t="str">
-        <f aca="false">Гонорары!$A$11</f>
-        <v>Ведущий / конферансье</v>
+        <f aca="false">Гонорары!$A$10</f>
+        <v>Разогрев / support act</v>
       </c>
       <c r="B46" s="64" t="n">
-        <f aca="false">-Гонорары!$E$11</f>
+        <f aca="false">-Гонорары!$E$10</f>
         <v>-0</v>
       </c>
       <c r="C46" s="65"/>
@@ -7416,11 +7485,11 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A47" s="63" t="str">
-        <f aca="false">Гонорары!$A$12</f>
-        <v>Налоги и взносы с гонораров</v>
+        <f aca="false">Гонорары!$A$11</f>
+        <v>Ведущий / конферансье</v>
       </c>
       <c r="B47" s="64" t="n">
-        <f aca="false">-Гонорары!$E$12</f>
+        <f aca="false">-Гонорары!$E$11</f>
         <v>-0</v>
       </c>
       <c r="C47" s="65"/>
@@ -7430,48 +7499,48 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="61" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="53"/>
-      <c r="C48" s="62" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)</f>
-        <v>-60000</v>
-      </c>
-      <c r="D48" s="21" t="n">
-        <f aca="false">IFERROR(C48/$C$6,0)</f>
-        <v>-0.128727740828148</v>
-      </c>
-      <c r="E48" s="53"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A48" s="63" t="str">
+        <f aca="false">Гонорары!$A$12</f>
+        <v>Налоги и взносы с гонораров</v>
+      </c>
+      <c r="B48" s="64" t="n">
+        <f aca="false">-Гонорары!$E$12</f>
+        <v>-0</v>
+      </c>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A49" s="63" t="str">
-        <f aca="false">Маркетинг!$A$6</f>
-        <v>Таргетированная реклама VK</v>
-      </c>
-      <c r="B49" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$6</f>
-        <v>-20000</v>
-      </c>
-      <c r="C49" s="65"/>
-      <c r="D49" s="65"/>
-      <c r="E49" s="65"/>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="53"/>
+      <c r="C49" s="62" t="n">
+        <f aca="false">-IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)</f>
+        <v>-60000</v>
+      </c>
+      <c r="D49" s="21" t="n">
+        <f aca="false">IFERROR(C49/$C$6,0)</f>
+        <v>-0.128727740828148</v>
+      </c>
+      <c r="E49" s="53"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A50" s="63" t="str">
-        <f aca="false">Маркетинг!$A$7</f>
-        <v>Посевы в Telegram-каналах</v>
+        <f aca="false">Маркетинг!$A$6</f>
+        <v>Таргетированная реклама VK</v>
       </c>
       <c r="B50" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$7</f>
-        <v>-15000</v>
+        <f aca="false">-Маркетинг!$B$6</f>
+        <v>-20000</v>
       </c>
       <c r="C50" s="65"/>
       <c r="D50" s="65"/>
@@ -7482,12 +7551,12 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A51" s="63" t="str">
-        <f aca="false">Маркетинг!$A$8</f>
-        <v>Блогеры и лидеры мнений</v>
+        <f aca="false">Маркетинг!$A$7</f>
+        <v>Посевы в Telegram-каналах</v>
       </c>
       <c r="B51" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$8</f>
-        <v>-10000</v>
+        <f aca="false">-Маркетинг!$B$7</f>
+        <v>-15000</v>
       </c>
       <c r="C51" s="65"/>
       <c r="D51" s="65"/>
@@ -7498,12 +7567,12 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A52" s="63" t="str">
-        <f aca="false">Маркетинг!$A$9</f>
-        <v>Наружная реклама и расклейка афиш</v>
+        <f aca="false">Маркетинг!$A$8</f>
+        <v>Блогеры и лидеры мнений</v>
       </c>
       <c r="B52" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$9</f>
-        <v>-5000</v>
+        <f aca="false">-Маркетинг!$B$8</f>
+        <v>-10000</v>
       </c>
       <c r="C52" s="65"/>
       <c r="D52" s="65"/>
@@ -7514,12 +7583,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A53" s="63" t="str">
-        <f aca="false">Маркетинг!$A$10</f>
-        <v>Городские афиши: Яндекс.Афиша, KudaGo</v>
+        <f aca="false">Маркетинг!$A$9</f>
+        <v>Наружная реклама и расклейка афиш</v>
       </c>
       <c r="B53" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$10</f>
-        <v>-0</v>
+        <f aca="false">-Маркетинг!$B$9</f>
+        <v>-5000</v>
       </c>
       <c r="C53" s="65"/>
       <c r="D53" s="65"/>
@@ -7530,12 +7599,12 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A54" s="63" t="str">
-        <f aca="false">Маркетинг!$A$11</f>
-        <v>PR: пресс-релиз, СМИ, интервью</v>
+        <f aca="false">Маркетинг!$A$10</f>
+        <v>Городские афиши: Яндекс.Афиша, KudaGo</v>
       </c>
       <c r="B54" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$11</f>
-        <v>-3000</v>
+        <f aca="false">-Маркетинг!$B$10</f>
+        <v>-0</v>
       </c>
       <c r="C54" s="65"/>
       <c r="D54" s="65"/>
@@ -7546,12 +7615,12 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A55" s="63" t="str">
-        <f aca="false">Маркетинг!$A$12</f>
-        <v>Email и база подписчиков</v>
+        <f aca="false">Маркетинг!$A$11</f>
+        <v>PR: пресс-релиз, СМИ, интервью</v>
       </c>
       <c r="B55" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$12</f>
-        <v>-1000</v>
+        <f aca="false">-Маркетинг!$B$11</f>
+        <v>-3000</v>
       </c>
       <c r="C55" s="65"/>
       <c r="D55" s="65"/>
@@ -7562,12 +7631,12 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A56" s="63" t="str">
-        <f aca="false">Маркетинг!$A$13</f>
-        <v>Продакшн контента: дизайн, тизер, фото</v>
+        <f aca="false">Маркетинг!$A$12</f>
+        <v>Email и база подписчиков</v>
       </c>
       <c r="B56" s="64" t="n">
-        <f aca="false">-Маркетинг!$B$13</f>
-        <v>-6000</v>
+        <f aca="false">-Маркетинг!$B$12</f>
+        <v>-1000</v>
       </c>
       <c r="C56" s="65"/>
       <c r="D56" s="65"/>
@@ -7576,47 +7645,47 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="B57" s="53"/>
-      <c r="C57" s="62" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Нет",Прочие!$E$19,0)</f>
-        <v>-76450</v>
-      </c>
-      <c r="D57" s="21" t="n">
-        <f aca="false">IFERROR(C57/$C$6,0)</f>
-        <v>-0.164020596438533</v>
-      </c>
-      <c r="E57" s="53"/>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
+      <c r="A57" s="63" t="str">
+        <f aca="false">Маркетинг!$A$13</f>
+        <v>Продакшн контента: дизайн, тизер, фото</v>
+      </c>
+      <c r="B57" s="64" t="n">
+        <f aca="false">-Маркетинг!$B$13</f>
+        <v>-6000</v>
+      </c>
+      <c r="C57" s="65"/>
+      <c r="D57" s="65"/>
+      <c r="E57" s="65"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
-      <c r="A58" s="63" t="str">
-        <f aca="false">Прочие!$A$5</f>
-        <v>Комиссия билетного оператора</v>
-      </c>
-      <c r="B58" s="64" t="n">
-        <f aca="false">-Прочие!$E$5</f>
-        <v>-0</v>
-      </c>
-      <c r="C58" s="65"/>
-      <c r="D58" s="65"/>
-      <c r="E58" s="65"/>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="53"/>
+      <c r="C58" s="62" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Нет",Прочие!$E$18,0)</f>
+        <v>-76450</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <f aca="false">IFERROR(C58/$C$6,0)</f>
+        <v>-0.164020596438533</v>
+      </c>
+      <c r="E58" s="53"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A59" s="63" t="str">
-        <f aca="false">Прочие!$A$6</f>
+        <f aca="false">Прочие!$A$5</f>
         <v>Полиграфия: афиши, флаеры</v>
       </c>
       <c r="B59" s="64" t="n">
-        <f aca="false">-Прочие!$E$6</f>
+        <f aca="false">-Прочие!$E$5</f>
         <v>-12000</v>
       </c>
       <c r="C59" s="65"/>
@@ -7628,11 +7697,11 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A60" s="63" t="str">
-        <f aca="false">Прочие!$A$7</f>
+        <f aca="false">Прочие!$A$6</f>
         <v>Бейджи, браслеты, программки</v>
       </c>
       <c r="B60" s="64" t="n">
-        <f aca="false">-Прочие!$E$7</f>
+        <f aca="false">-Прочие!$E$6</f>
         <v>-5000</v>
       </c>
       <c r="C60" s="65"/>
@@ -7644,11 +7713,11 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A61" s="63" t="str">
-        <f aca="false">Прочие!$A$8</f>
+        <f aca="false">Прочие!$A$7</f>
         <v>Оформление сцены и зала, декор</v>
       </c>
       <c r="B61" s="64" t="n">
-        <f aca="false">-Прочие!$E$8</f>
+        <f aca="false">-Прочие!$E$7</f>
         <v>-0</v>
       </c>
       <c r="C61" s="65"/>
@@ -7660,11 +7729,11 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A62" s="63" t="str">
-        <f aca="false">Прочие!$A$9</f>
+        <f aca="false">Прочие!$A$8</f>
         <v>Репетиции, аренда репбазы</v>
       </c>
       <c r="B62" s="64" t="n">
-        <f aca="false">-Прочие!$E$9</f>
+        <f aca="false">-Прочие!$E$8</f>
         <v>-12000</v>
       </c>
       <c r="C62" s="65"/>
@@ -7676,11 +7745,11 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A63" s="63" t="str">
-        <f aca="false">Прочие!$A$10</f>
+        <f aca="false">Прочие!$A$9</f>
         <v>Транспорт оборудования</v>
       </c>
       <c r="B63" s="64" t="n">
-        <f aca="false">-Прочие!$E$10</f>
+        <f aca="false">-Прочие!$E$9</f>
         <v>-12000</v>
       </c>
       <c r="C63" s="65"/>
@@ -7692,11 +7761,11 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A64" s="63" t="str">
-        <f aca="false">Прочие!$A$11</f>
+        <f aca="false">Прочие!$A$10</f>
         <v>Трансфер и проживание команды</v>
       </c>
       <c r="B64" s="64" t="n">
-        <f aca="false">-Прочие!$E$11</f>
+        <f aca="false">-Прочие!$E$10</f>
         <v>-0</v>
       </c>
       <c r="C64" s="65"/>
@@ -7708,11 +7777,11 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A65" s="63" t="str">
-        <f aca="false">Прочие!$A$12</f>
+        <f aca="false">Прочие!$A$11</f>
         <v>Кейтеринг и райдер бэкстейджа</v>
       </c>
       <c r="B65" s="64" t="n">
-        <f aca="false">-Прочие!$E$12</f>
+        <f aca="false">-Прочие!$E$11</f>
         <v>-10500</v>
       </c>
       <c r="C65" s="65"/>
@@ -7724,11 +7793,11 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A66" s="63" t="str">
-        <f aca="false">Прочие!$A$13</f>
+        <f aca="false">Прочие!$A$12</f>
         <v>Фотограф</v>
       </c>
       <c r="B66" s="64" t="n">
-        <f aca="false">-Прочие!$E$13</f>
+        <f aca="false">-Прочие!$E$12</f>
         <v>-12000</v>
       </c>
       <c r="C66" s="65"/>
@@ -7740,11 +7809,11 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A67" s="63" t="str">
-        <f aca="false">Прочие!$A$14</f>
+        <f aca="false">Прочие!$A$13</f>
         <v>Видеосъёмка концерта</v>
       </c>
       <c r="B67" s="64" t="n">
-        <f aca="false">-Прочие!$E$14</f>
+        <f aca="false">-Прочие!$E$13</f>
         <v>-0</v>
       </c>
       <c r="C67" s="65"/>
@@ -7756,11 +7825,11 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A68" s="63" t="str">
-        <f aca="false">Прочие!$A$15</f>
+        <f aca="false">Прочие!$A$14</f>
         <v>Юридическое сопровождение</v>
       </c>
       <c r="B68" s="64" t="n">
-        <f aca="false">-Прочие!$E$15</f>
+        <f aca="false">-Прочие!$E$14</f>
         <v>-6000</v>
       </c>
       <c r="C68" s="65"/>
@@ -7772,11 +7841,11 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A69" s="63" t="str">
-        <f aca="false">Прочие!$A$16</f>
+        <f aca="false">Прочие!$A$15</f>
         <v>Онлайн-касса, ОФД</v>
       </c>
       <c r="B69" s="64" t="n">
-        <f aca="false">-Прочие!$E$16</f>
+        <f aca="false">-Прочие!$E$15</f>
         <v>-0</v>
       </c>
       <c r="C69" s="65"/>
@@ -7788,11 +7857,11 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A70" s="63" t="str">
-        <f aca="false">Прочие!$A$17</f>
+        <f aca="false">Прочие!$A$16</f>
         <v>Страхование мероприятия</v>
       </c>
       <c r="B70" s="64" t="n">
-        <f aca="false">-Прочие!$E$17</f>
+        <f aca="false">-Прочие!$E$16</f>
         <v>-0</v>
       </c>
       <c r="C70" s="65"/>
@@ -7804,11 +7873,11 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A71" s="63" t="str">
-        <f aca="false">Прочие!$A$18</f>
+        <f aca="false">Прочие!$A$17</f>
         <v>Резерв на непредвиденное</v>
       </c>
       <c r="B71" s="64" t="n">
-        <f aca="false">-Прочие!$E$18</f>
+        <f aca="false">-Прочие!$E$17</f>
         <v>-6950</v>
       </c>
       <c r="C71" s="65"/>
@@ -7820,16 +7889,16 @@
     </row>
     <row r="72" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="73" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B72" s="51"/>
       <c r="C72" s="74" t="n">
-        <f aca="false">Экономика!$C$34+Экономика!$C$37+Экономика!$C$38+Экономика!$C$39+Экономика!$C$48+Экономика!$C$57</f>
-        <v>-72130.84</v>
+        <f aca="false">Экономика!$C$35+Экономика!$C$38+Экономика!$C$39+Экономика!$C$40+Экономика!$C$49+Экономика!$C$58</f>
+        <v>-82851.14</v>
       </c>
       <c r="D72" s="75" t="n">
         <f aca="false">IFERROR(C72/$C$6,0)</f>
-        <v>-0.154754001287277</v>
+        <v>-0.177754001287277</v>
       </c>
       <c r="E72" s="51"/>
       <c r="F72" s="4"/>
@@ -7848,7 +7917,7 @@
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -7860,11 +7929,11 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="60" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B75" s="53"/>
       <c r="C75" s="47" t="n">
-        <f aca="false">(IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)+IF(Вводные!$B$37="Да",Гонорары!$E$13,0)+IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)+IF(Вводные!$B$39="Да",Прочие!$E$19,0))</f>
+        <f aca="false">(IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)+IF(Вводные!$B$39="Да",Гонорары!$E$13,0)+IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)+IF(Вводные!$B$41="Да",Прочие!$E$18,0))</f>
         <v>154500</v>
       </c>
       <c r="D75" s="53"/>
@@ -7875,11 +7944,11 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="60" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B76" s="53"/>
       <c r="C76" s="47" t="n">
-        <f aca="false">(IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)+IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)+IF(Вводные!$B$39="Нет",Прочие!$E$19,0))</f>
+        <f aca="false">(IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)+IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)+IF(Вводные!$B$41="Нет",Прочие!$E$18,0))</f>
         <v>185450</v>
       </c>
       <c r="D76" s="53"/>
@@ -7890,16 +7959,16 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="61" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B77" s="53"/>
       <c r="C77" s="62" t="n">
-        <f aca="false">IFERROR(((IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)+IF(Вводные!$B$37="Да",Гонорары!$E$13,0)+IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)+IF(Вводные!$B$39="Да",Прочие!$E$19,0))+(IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)+IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)+IF(Вводные!$B$39="Нет",Прочие!$E$19,0))/((1-Вводные!$B$33)*Вводные!$B$26))/(1-Вводные!$B$18-Вводные!$B$19),0)</f>
-        <v>648432.760364004</v>
+        <f aca="false">IFERROR(((IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)+IF(Вводные!$B$39="Да",Гонорары!$E$13,0)+IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)+IF(Вводные!$B$41="Да",Прочие!$E$18,0))+(IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)+IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)+IF(Вводные!$B$41="Нет",Прочие!$E$18,0))/((1-Вводные!$B$35)*Вводные!$B$28))/(1-Вводные!$B$18-Вводные!$B$21-Вводные!$B$19*IF(Вводные!$B$20="Валовой сбор",1,1-Вводные!$B$18)),0)</f>
+        <v>688459.47396672</v>
       </c>
       <c r="D77" s="53"/>
       <c r="E77" s="37" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -7907,12 +7976,12 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="61" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B78" s="53"/>
       <c r="C78" s="76" t="n">
         <f aca="false">IFERROR(ROUNDUP(Экономика!$C$77/Билеты!$B$19,0),0)</f>
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D78" s="53"/>
       <c r="E78" s="53"/>
@@ -7922,12 +7991,12 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="61" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B79" s="53"/>
       <c r="C79" s="77" t="n">
         <f aca="false">IFERROR(Экономика!$C$78/Билеты!$B$22/Вводные!$B$12,0)</f>
-        <v>0.939861111111111</v>
+        <v>0.995972222222222</v>
       </c>
       <c r="D79" s="53"/>
       <c r="E79" s="53"/>
@@ -7937,16 +8006,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="60" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B80" s="53"/>
       <c r="C80" s="28" t="n">
         <f aca="false">IFERROR((Билеты!$B$17-Экономика!$C$78)/Билеты!$B$17,0)</f>
-        <v>-0.395833333333333</v>
+        <v>-0.479166666666667</v>
       </c>
       <c r="D80" s="53"/>
       <c r="E80" s="37" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -7954,12 +8023,12 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="60" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B81" s="53"/>
       <c r="C81" s="28" t="n">
         <f aca="false">IFERROR(Экономика!$C$72/Экономика!$C$6,0)</f>
-        <v>-0.154754001287277</v>
+        <v>-0.177754001287277</v>
       </c>
       <c r="D81" s="53"/>
       <c r="E81" s="53"/>
@@ -7969,12 +8038,12 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="60" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B82" s="53"/>
       <c r="C82" s="47" t="n">
         <f aca="false">IFERROR(Экономика!$C$72/Билеты!$E$12,0)</f>
-        <v>-357.083366336634</v>
+        <v>-410.154158415842</v>
       </c>
       <c r="D82" s="53"/>
       <c r="E82" s="53"/>
@@ -7984,12 +8053,12 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="61" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B83" s="53"/>
       <c r="C83" s="78" t="str">
         <f aca="false">IF(Экономика!$C$72&lt;0,"УБЫТОК. Нужен сбор от "&amp;TEXT(Экономика!$C$77,"# ##0")&amp;" ₽ ("&amp;TEXT(Экономика!$C$79,"0%")&amp;" зала), чтобы выйти в ноль",IF(Экономика!$C$80&lt;0.15,"НА ГРАНИ. Запас прочности меньше 15%",IF(Экономика!$C$81&lt;0.1,"СЛАБО. Рентабельность ниже 10% от сбора","ЗДОРОВО. Проект окупается с запасом")))</f>
-        <v>УБЫТОК. Нужен сбор от 648 433 ₽ (94% зала), чтобы выйти в ноль</v>
+        <v>УБЫТОК. Нужен сбор от 688 459 ₽ (100% зала), чтобы выйти в ноль</v>
       </c>
       <c r="D83" s="53"/>
       <c r="E83" s="53"/>
@@ -8021,7 +8090,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -8032,7 +8101,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8044,7 +8113,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8066,31 +8135,31 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B5" s="79" t="n">
         <f aca="false">Вводные!$B$13</f>
@@ -8110,16 +8179,16 @@
       </c>
       <c r="F5" s="79" t="n">
         <f aca="false">Экономика!$C$79</f>
-        <v>0.939861111111111</v>
+        <v>0.995972222222222</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B6" s="81" t="n">
         <f aca="false">ROUND(Вводные!$B$12*B5,0)</f>
@@ -8139,14 +8208,14 @@
       </c>
       <c r="F6" s="81" t="n">
         <f aca="false">ROUND(Вводные!$B$12*F5,0)</f>
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B7" s="81" t="n">
         <f aca="false">ROUND(B6*Билеты!$B$22,0)</f>
@@ -8166,14 +8235,14 @@
       </c>
       <c r="F7" s="81" t="n">
         <f aca="false">ROUND(F6*Билеты!$B$22,0)</f>
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B8" s="49" t="n">
         <f aca="false">Билеты!$B$19</f>
@@ -8200,7 +8269,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B9" s="41" t="n">
         <f aca="false">B7*B8</f>
@@ -8220,14 +8289,14 @@
       </c>
       <c r="F9" s="41" t="n">
         <f aca="false">F7*F8</f>
-        <v>650597.916666667</v>
+        <v>689439.583333333</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">-B9*Вводные!$B$18</f>
@@ -8247,114 +8316,114 @@
       </c>
       <c r="F10" s="49" t="n">
         <f aca="false">-F9*Вводные!$B$18</f>
-        <v>-39035.875</v>
+        <v>-41366.375</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B11" s="49" t="n">
-        <f aca="false">-B9*Вводные!$B$19</f>
-        <v>-22139.75</v>
+        <f aca="false">-IF(Вводные!$B$20="Валовой сбор",B9,B9*(1-Вводные!$B$18))*Вводные!$B$19</f>
+        <v>-13837.34375</v>
       </c>
       <c r="C11" s="83" t="n">
-        <f aca="false">-C9*Вводные!$B$19</f>
-        <v>-37288</v>
+        <f aca="false">-IF(Вводные!$B$20="Валовой сбор",C9,C9*(1-Вводные!$B$18))*Вводные!$B$19</f>
+        <v>-23305</v>
       </c>
       <c r="D11" s="49" t="n">
-        <f aca="false">-D9*Вводные!$B$19</f>
-        <v>-49911.5416666667</v>
+        <f aca="false">-IF(Вводные!$B$20="Валовой сбор",D9,D9*(1-Вводные!$B$18))*Вводные!$B$19</f>
+        <v>-31194.7135416667</v>
       </c>
       <c r="E11" s="49" t="n">
-        <f aca="false">-E9*Вводные!$B$19</f>
-        <v>-55349.375</v>
+        <f aca="false">-IF(Вводные!$B$20="Валовой сбор",E9,E9*(1-Вводные!$B$18))*Вводные!$B$19</f>
+        <v>-34593.359375</v>
       </c>
       <c r="F11" s="49" t="n">
-        <f aca="false">-F9*Вводные!$B$19</f>
-        <v>-52047.8333333333</v>
+        <f aca="false">-IF(Вводные!$B$20="Валовой сбор",F9,F9*(1-Вводные!$B$18))*Вводные!$B$19</f>
+        <v>-34471.9791666667</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B12" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)</f>
-        <v>-154500</v>
+        <f aca="false">-B9*Вводные!$B$21</f>
+        <v>-22139.75</v>
       </c>
       <c r="C12" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)</f>
-        <v>-154500</v>
+        <f aca="false">-C9*Вводные!$B$21</f>
+        <v>-37288</v>
       </c>
       <c r="D12" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)</f>
-        <v>-154500</v>
+        <f aca="false">-D9*Вводные!$B$21</f>
+        <v>-49911.5416666667</v>
       </c>
       <c r="E12" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)</f>
-        <v>-154500</v>
+        <f aca="false">-E9*Вводные!$B$21</f>
+        <v>-55349.375</v>
       </c>
       <c r="F12" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$22="Фиксированной суммой",Вводные!$B$23,Технические!$E$22)</f>
-        <v>-154500</v>
+        <f aca="false">-F9*Вводные!$B$21</f>
+        <v>-55155.1666666667</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B13" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Да",Гонорары!$E$13,0)</f>
-        <v>-0</v>
+        <f aca="false">-IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)</f>
+        <v>-154500</v>
       </c>
       <c r="C13" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Да",Гонорары!$E$13,0)</f>
-        <v>-0</v>
+        <f aca="false">-IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)</f>
+        <v>-154500</v>
       </c>
       <c r="D13" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Да",Гонорары!$E$13,0)</f>
-        <v>-0</v>
+        <f aca="false">-IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)</f>
+        <v>-154500</v>
       </c>
       <c r="E13" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Да",Гонорары!$E$13,0)</f>
-        <v>-0</v>
+        <f aca="false">-IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)</f>
+        <v>-154500</v>
       </c>
       <c r="F13" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Да",Гонорары!$E$13,0)</f>
-        <v>-0</v>
+        <f aca="false">-IF(Вводные!$B$24="Фиксированной суммой",Вводные!$B$25,Технические!$E$22)</f>
+        <v>-154500</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B14" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)</f>
+        <f aca="false">-IF(Вводные!$B$39="Да",Гонорары!$E$13,0)</f>
         <v>-0</v>
       </c>
       <c r="C14" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)</f>
+        <f aca="false">-IF(Вводные!$B$39="Да",Гонорары!$E$13,0)</f>
         <v>-0</v>
       </c>
       <c r="D14" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)</f>
+        <f aca="false">-IF(Вводные!$B$39="Да",Гонорары!$E$13,0)</f>
         <v>-0</v>
       </c>
       <c r="E14" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)</f>
+        <f aca="false">-IF(Вводные!$B$39="Да",Гонорары!$E$13,0)</f>
         <v>-0</v>
       </c>
       <c r="F14" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Да",Маркетинг!$B$14,0)</f>
+        <f aca="false">-IF(Вводные!$B$39="Да",Гонорары!$E$13,0)</f>
         <v>-0</v>
       </c>
       <c r="G14" s="4"/>
@@ -8362,346 +8431,373 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B15" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Да",Прочие!$E$19,0)</f>
+        <f aca="false">-IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)</f>
         <v>-0</v>
       </c>
       <c r="C15" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Да",Прочие!$E$19,0)</f>
+        <f aca="false">-IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)</f>
         <v>-0</v>
       </c>
       <c r="D15" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Да",Прочие!$E$19,0)</f>
+        <f aca="false">-IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)</f>
         <v>-0</v>
       </c>
       <c r="E15" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Да",Прочие!$E$19,0)</f>
+        <f aca="false">-IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)</f>
         <v>-0</v>
       </c>
       <c r="F15" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Да",Прочие!$E$19,0)</f>
+        <f aca="false">-IF(Вводные!$B$40="Да",Маркетинг!$B$14,0)</f>
         <v>-0</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="B16" s="41" t="n">
-        <f aca="false">SUM(B9:B15)</f>
-        <v>83502.3125</v>
-      </c>
-      <c r="C16" s="84" t="n">
-        <f aca="false">SUM(C9:C15)</f>
-        <v>246346</v>
-      </c>
-      <c r="D16" s="41" t="n">
-        <f aca="false">SUM(D9:D15)</f>
-        <v>382049.072916667</v>
-      </c>
-      <c r="E16" s="41" t="n">
-        <f aca="false">SUM(E9:E15)</f>
-        <v>440505.78125</v>
-      </c>
-      <c r="F16" s="41" t="n">
-        <f aca="false">SUM(F9:F15)</f>
-        <v>405014.208333333</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>292</v>
-      </c>
+      <c r="A16" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Да",Прочие!$E$18,0)</f>
+        <v>-0</v>
+      </c>
+      <c r="C16" s="83" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Да",Прочие!$E$18,0)</f>
+        <v>-0</v>
+      </c>
+      <c r="D16" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Да",Прочие!$E$18,0)</f>
+        <v>-0</v>
+      </c>
+      <c r="E16" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Да",Прочие!$E$18,0)</f>
+        <v>-0</v>
+      </c>
+      <c r="F16" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Да",Прочие!$E$18,0)</f>
+        <v>-0</v>
+      </c>
+      <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="49" t="n">
-        <f aca="false">-IF(B16&gt;=0,B16*Вводные!$B$27,IF(Вводные!$B$28="Да",B16*Вводные!$B$27,0))</f>
-        <v>-41751.15625</v>
-      </c>
-      <c r="C17" s="83" t="n">
-        <f aca="false">-IF(C16&gt;=0,C16*Вводные!$B$27,IF(Вводные!$B$28="Да",C16*Вводные!$B$27,0))</f>
-        <v>-123173</v>
-      </c>
-      <c r="D17" s="49" t="n">
-        <f aca="false">-IF(D16&gt;=0,D16*Вводные!$B$27,IF(Вводные!$B$28="Да",D16*Вводные!$B$27,0))</f>
-        <v>-191024.536458333</v>
-      </c>
-      <c r="E17" s="49" t="n">
-        <f aca="false">-IF(E16&gt;=0,E16*Вводные!$B$27,IF(Вводные!$B$28="Да",E16*Вводные!$B$27,0))</f>
-        <v>-220252.890625</v>
-      </c>
-      <c r="F17" s="49" t="n">
-        <f aca="false">-IF(F16&gt;=0,F16*Вводные!$B$27,IF(Вводные!$B$28="Да",F16*Вводные!$B$27,0))</f>
-        <v>-202507.104166667</v>
-      </c>
-      <c r="G17" s="4"/>
+      <c r="A17" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17" s="41" t="n">
+        <f aca="false">SUM(B9:B16)</f>
+        <v>69664.96875</v>
+      </c>
+      <c r="C17" s="84" t="n">
+        <f aca="false">SUM(C9:C16)</f>
+        <v>223041</v>
+      </c>
+      <c r="D17" s="41" t="n">
+        <f aca="false">SUM(D9:D16)</f>
+        <v>350854.359375</v>
+      </c>
+      <c r="E17" s="41" t="n">
+        <f aca="false">SUM(E9:E16)</f>
+        <v>405912.421875</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <f aca="false">SUM(F9:F16)</f>
+        <v>403946.0625</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B18" s="85" t="n">
-        <f aca="false">B16+B17</f>
-        <v>41751.15625</v>
-      </c>
-      <c r="C18" s="86" t="n">
-        <f aca="false">C16+C17</f>
-        <v>123173</v>
-      </c>
-      <c r="D18" s="85" t="n">
-        <f aca="false">D16+D17</f>
-        <v>191024.536458333</v>
-      </c>
-      <c r="E18" s="85" t="n">
-        <f aca="false">E16+E17</f>
-        <v>220252.890625</v>
-      </c>
-      <c r="F18" s="85" t="n">
-        <f aca="false">F16+F17</f>
-        <v>202507.104166667</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>294</v>
-      </c>
+      <c r="A18" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">-IF(B17&gt;=0,B17*Вводные!$B$29,IF(Вводные!$B$30="Да",B17*Вводные!$B$29,0))</f>
+        <v>-34832.484375</v>
+      </c>
+      <c r="C18" s="83" t="n">
+        <f aca="false">-IF(C17&gt;=0,C17*Вводные!$B$29,IF(Вводные!$B$30="Да",C17*Вводные!$B$29,0))</f>
+        <v>-111520.5</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <f aca="false">-IF(D17&gt;=0,D17*Вводные!$B$29,IF(Вводные!$B$30="Да",D17*Вводные!$B$29,0))</f>
+        <v>-175427.1796875</v>
+      </c>
+      <c r="E18" s="49" t="n">
+        <f aca="false">-IF(E17&gt;=0,E17*Вводные!$B$29,IF(Вводные!$B$30="Да",E17*Вводные!$B$29,0))</f>
+        <v>-202956.2109375</v>
+      </c>
+      <c r="F18" s="49" t="n">
+        <f aca="false">-IF(F17&gt;=0,F17*Вводные!$B$29,IF(Вводные!$B$30="Да",F17*Вводные!$B$29,0))</f>
+        <v>-201973.03125</v>
+      </c>
+      <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">-MAX(0,B18)*Вводные!$B$31</f>
-        <v>-2922.5809375</v>
-      </c>
-      <c r="C19" s="83" t="n">
-        <f aca="false">-MAX(0,C18)*Вводные!$B$31</f>
-        <v>-8622.11</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <f aca="false">-MAX(0,D18)*Вводные!$B$31</f>
-        <v>-13371.7175520833</v>
-      </c>
-      <c r="E19" s="49" t="n">
-        <f aca="false">-MAX(0,E18)*Вводные!$B$31</f>
-        <v>-15417.70234375</v>
-      </c>
-      <c r="F19" s="49" t="n">
-        <f aca="false">-MAX(0,F18)*Вводные!$B$31</f>
-        <v>-14175.4972916667</v>
-      </c>
-      <c r="G19" s="4"/>
+      <c r="A19" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B19" s="85" t="n">
+        <f aca="false">B17+B18</f>
+        <v>34832.484375</v>
+      </c>
+      <c r="C19" s="86" t="n">
+        <f aca="false">C17+C18</f>
+        <v>111520.5</v>
+      </c>
+      <c r="D19" s="85" t="n">
+        <f aca="false">D17+D18</f>
+        <v>175427.1796875</v>
+      </c>
+      <c r="E19" s="85" t="n">
+        <f aca="false">E17+E18</f>
+        <v>202956.2109375</v>
+      </c>
+      <c r="F19" s="85" t="n">
+        <f aca="false">F17+F18</f>
+        <v>201973.03125</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B20" s="49" t="n">
-        <f aca="false">-MAX(0,B18)*Вводные!$B$32</f>
-        <v>-417.5115625</v>
+        <f aca="false">-MAX(0,B19)*Вводные!$B$33</f>
+        <v>-2438.27390625</v>
       </c>
       <c r="C20" s="83" t="n">
-        <f aca="false">-MAX(0,C18)*Вводные!$B$32</f>
-        <v>-1231.73</v>
+        <f aca="false">-MAX(0,C19)*Вводные!$B$33</f>
+        <v>-7806.435</v>
       </c>
       <c r="D20" s="49" t="n">
-        <f aca="false">-MAX(0,D18)*Вводные!$B$32</f>
-        <v>-1910.24536458333</v>
+        <f aca="false">-MAX(0,D19)*Вводные!$B$33</f>
+        <v>-12279.902578125</v>
       </c>
       <c r="E20" s="49" t="n">
-        <f aca="false">-MAX(0,E18)*Вводные!$B$32</f>
-        <v>-2202.52890625</v>
+        <f aca="false">-MAX(0,E19)*Вводные!$B$33</f>
+        <v>-14206.934765625</v>
       </c>
       <c r="F20" s="49" t="n">
-        <f aca="false">-MAX(0,F18)*Вводные!$B$32</f>
-        <v>-2025.07104166667</v>
+        <f aca="false">-MAX(0,F19)*Вводные!$B$33</f>
+        <v>-14138.1121875</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B21" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)</f>
-        <v>-49000</v>
+        <f aca="false">-MAX(0,B19)*Вводные!$B$34</f>
+        <v>-348.32484375</v>
       </c>
       <c r="C21" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)</f>
-        <v>-49000</v>
+        <f aca="false">-MAX(0,C19)*Вводные!$B$34</f>
+        <v>-1115.205</v>
       </c>
       <c r="D21" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)</f>
-        <v>-49000</v>
+        <f aca="false">-MAX(0,D19)*Вводные!$B$34</f>
+        <v>-1754.271796875</v>
       </c>
       <c r="E21" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)</f>
-        <v>-49000</v>
+        <f aca="false">-MAX(0,E19)*Вводные!$B$34</f>
+        <v>-2029.562109375</v>
       </c>
       <c r="F21" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$37="Нет",Гонорары!$E$13,0)</f>
-        <v>-49000</v>
+        <f aca="false">-MAX(0,F19)*Вводные!$B$34</f>
+        <v>-2019.7303125</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B22" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)</f>
-        <v>-60000</v>
+        <f aca="false">-IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)</f>
+        <v>-49000</v>
       </c>
       <c r="C22" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)</f>
-        <v>-60000</v>
+        <f aca="false">-IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)</f>
+        <v>-49000</v>
       </c>
       <c r="D22" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)</f>
-        <v>-60000</v>
+        <f aca="false">-IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)</f>
+        <v>-49000</v>
       </c>
       <c r="E22" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)</f>
-        <v>-60000</v>
+        <f aca="false">-IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)</f>
+        <v>-49000</v>
       </c>
       <c r="F22" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$38="Нет",Маркетинг!$B$14,0)</f>
-        <v>-60000</v>
+        <f aca="false">-IF(Вводные!$B$39="Нет",Гонорары!$E$13,0)</f>
+        <v>-49000</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B23" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Нет",Прочие!$E$19,0)</f>
-        <v>-76450</v>
+        <f aca="false">-IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)</f>
+        <v>-60000</v>
       </c>
       <c r="C23" s="83" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Нет",Прочие!$E$19,0)</f>
-        <v>-76450</v>
+        <f aca="false">-IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)</f>
+        <v>-60000</v>
       </c>
       <c r="D23" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Нет",Прочие!$E$19,0)</f>
-        <v>-76450</v>
+        <f aca="false">-IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)</f>
+        <v>-60000</v>
       </c>
       <c r="E23" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Нет",Прочие!$E$19,0)</f>
-        <v>-76450</v>
+        <f aca="false">-IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)</f>
+        <v>-60000</v>
       </c>
       <c r="F23" s="49" t="n">
-        <f aca="false">-IF(Вводные!$B$39="Нет",Прочие!$E$19,0)</f>
-        <v>-76450</v>
+        <f aca="false">-IF(Вводные!$B$40="Нет",Маркетинг!$B$14,0)</f>
+        <v>-60000</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="87" t="n">
-        <f aca="false">B18+SUM(B19:B23)</f>
-        <v>-147038.93625</v>
-      </c>
-      <c r="C24" s="88" t="n">
-        <f aca="false">C18+SUM(C19:C23)</f>
-        <v>-72130.84</v>
-      </c>
-      <c r="D24" s="87" t="n">
-        <f aca="false">D18+SUM(D19:D23)</f>
-        <v>-9707.42645833336</v>
-      </c>
-      <c r="E24" s="87" t="n">
-        <f aca="false">E18+SUM(E19:E23)</f>
-        <v>17182.659375</v>
-      </c>
-      <c r="F24" s="87" t="n">
-        <f aca="false">F18+SUM(F19:F23)</f>
-        <v>856.535833333299</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>300</v>
-      </c>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B24" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Нет",Прочие!$E$18,0)</f>
+        <v>-76450</v>
+      </c>
+      <c r="C24" s="83" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Нет",Прочие!$E$18,0)</f>
+        <v>-76450</v>
+      </c>
+      <c r="D24" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Нет",Прочие!$E$18,0)</f>
+        <v>-76450</v>
+      </c>
+      <c r="E24" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Нет",Прочие!$E$18,0)</f>
+        <v>-76450</v>
+      </c>
+      <c r="F24" s="49" t="n">
+        <f aca="false">-IF(Вводные!$B$41="Нет",Прочие!$E$18,0)</f>
+        <v>-76450</v>
+      </c>
+      <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" s="79" t="n">
-        <f aca="false">IFERROR(B24/B9,0)</f>
-        <v>-0.531312002168046</v>
-      </c>
-      <c r="C25" s="80" t="n">
-        <f aca="false">IFERROR(C24/C9,0)</f>
-        <v>-0.154754001287277</v>
-      </c>
-      <c r="D25" s="79" t="n">
-        <f aca="false">IFERROR(D24/D9,0)</f>
-        <v>-0.0155594095220127</v>
-      </c>
-      <c r="E25" s="79" t="n">
-        <f aca="false">IFERROR(E24/E9,0)</f>
-        <v>0.0248351991327815</v>
-      </c>
-      <c r="F25" s="79" t="n">
-        <f aca="false">IFERROR(F24/F9,0)</f>
-        <v>0.00131653639120419</v>
-      </c>
-      <c r="G25" s="4"/>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="87" t="n">
+        <f aca="false">B19+SUM(B20:B24)</f>
+        <v>-153404.114375</v>
+      </c>
+      <c r="C25" s="88" t="n">
+        <f aca="false">C19+SUM(C20:C24)</f>
+        <v>-82851.14</v>
+      </c>
+      <c r="D25" s="87" t="n">
+        <f aca="false">D19+SUM(D20:D24)</f>
+        <v>-24056.9946875</v>
+      </c>
+      <c r="E25" s="87" t="n">
+        <f aca="false">E19+SUM(E20:E24)</f>
+        <v>1269.71406249999</v>
+      </c>
+      <c r="F25" s="87" t="n">
+        <f aca="false">F19+SUM(F20:F24)</f>
+        <v>365.188749999943</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B26" s="49" t="n">
-        <f aca="false">B24-$C$24</f>
-        <v>-74908.09625</v>
-      </c>
-      <c r="C26" s="49" t="n">
-        <f aca="false">C24-$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="49" t="n">
-        <f aca="false">D24-$C$24</f>
-        <v>62423.4135416666</v>
-      </c>
-      <c r="E26" s="49" t="n">
-        <f aca="false">E24-$C$24</f>
-        <v>89313.499375</v>
-      </c>
-      <c r="F26" s="49" t="n">
-        <f aca="false">F24-$C$24</f>
-        <v>72987.3758333333</v>
+        <v>285</v>
+      </c>
+      <c r="B26" s="79" t="n">
+        <f aca="false">IFERROR(B25/B9,0)</f>
+        <v>-0.554312002168046</v>
+      </c>
+      <c r="C26" s="80" t="n">
+        <f aca="false">IFERROR(C25/C9,0)</f>
+        <v>-0.177754001287277</v>
+      </c>
+      <c r="D26" s="79" t="n">
+        <f aca="false">IFERROR(D25/D9,0)</f>
+        <v>-0.0385594095220128</v>
+      </c>
+      <c r="E26" s="79" t="n">
+        <f aca="false">IFERROR(E25/E9,0)</f>
+        <v>0.00183519913278152</v>
+      </c>
+      <c r="F26" s="79" t="n">
+        <f aca="false">IFERROR(F25/F9,0)</f>
+        <v>0.000529689270572937</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" s="49" t="n">
+        <f aca="false">B25-$C$25</f>
+        <v>-70552.974375</v>
+      </c>
+      <c r="C27" s="49" t="n">
+        <f aca="false">C25-$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="49" t="n">
+        <f aca="false">D25-$C$25</f>
+        <v>58794.1453125</v>
+      </c>
+      <c r="E27" s="49" t="n">
+        <f aca="false">E25-$C$25</f>
+        <v>84120.8540625</v>
+      </c>
+      <c r="F27" s="49" t="n">
+        <f aca="false">F25-$C$25</f>
+        <v>83216.32875</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B24:F24">
+  <conditionalFormatting sqref="B25:F25">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:F16">
+  <conditionalFormatting sqref="B17:F17">
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18:F18">
+  <conditionalFormatting sqref="B19:F19">
     <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
